--- a/unit-tests/test-report.xlsx
+++ b/unit-tests/test-report.xlsx
@@ -442,7 +442,7 @@
         <v>Execution Timestamp</v>
       </c>
       <c r="B5" t="str">
-        <v>6/8/2026, 9:43:19 am</v>
+        <v>6/8/2026, 9:58:12 am</v>
       </c>
       <c r="C5" t="str">
         <v>Local System Time</v>
@@ -497,7 +497,7 @@
         <v>Total Suite Duration</v>
       </c>
       <c r="B10" t="str">
-        <v>0.106 seconds</v>
+        <v>0.019 seconds</v>
       </c>
       <c r="C10" t="str">
         <v>Cumulative test execution time</v>
@@ -645,10 +645,10 @@
         <v>PASS</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G2" t="str">
-        <v>2026-08-06T04:13:19.079Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="3">
@@ -668,10 +668,10 @@
         <v>PASS</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="4">
@@ -691,10 +691,10 @@
         <v>PASS</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G4" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="5">
@@ -714,10 +714,10 @@
         <v>PASS</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G5" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="6">
@@ -737,10 +737,10 @@
         <v>PASS</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G6" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="7">
@@ -760,10 +760,10 @@
         <v>PASS</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G7" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="8">
@@ -786,7 +786,7 @@
         <v>8</v>
       </c>
       <c r="G8" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="9">
@@ -800,16 +800,16 @@
         <v>01_domain_models.test.js</v>
       </c>
       <c r="D9" t="str">
-        <v>UNIT-008: Appointment Status State Machine - SCHEDULED -&gt; CONFIRMED Transition</v>
+        <v>UNIT-008: Appointment Status State Machine - SCHEDULED to CONFIRMED Transition</v>
       </c>
       <c r="E9" t="str">
         <v>PASS</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G9" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="10">
@@ -823,16 +823,16 @@
         <v>01_domain_models.test.js</v>
       </c>
       <c r="D10" t="str">
-        <v>UNIT-009: Appointment Status State Machine - CONFIRMED -&gt; COMPLETED Transition</v>
+        <v>UNIT-009: Appointment Status State Machine - CONFIRMED to COMPLETED Transition</v>
       </c>
       <c r="E10" t="str">
         <v>PASS</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G10" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="11">
@@ -846,7 +846,7 @@
         <v>01_domain_models.test.js</v>
       </c>
       <c r="D11" t="str">
-        <v>UNIT-010: Appointment Status State Machine - Prevent Invalid COMPLETED -&gt; SCHEDULED Reversion</v>
+        <v>UNIT-010: Appointment Status State Machine - Prevent Invalid COMPLETED to SCHEDULED Reversion</v>
       </c>
       <c r="E11" t="str">
         <v>PASS</v>
@@ -855,7 +855,7 @@
         <v>5</v>
       </c>
       <c r="G11" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="12">
@@ -875,10 +875,10 @@
         <v>PASS</v>
       </c>
       <c r="F12">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G12" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="13">
@@ -898,10 +898,10 @@
         <v>PASS</v>
       </c>
       <c r="F13">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G13" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="14">
@@ -921,10 +921,10 @@
         <v>PASS</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G14" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="15">
@@ -944,10 +944,10 @@
         <v>PASS</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="16">
@@ -967,10 +967,10 @@
         <v>PASS</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G16" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="17">
@@ -990,10 +990,10 @@
         <v>PASS</v>
       </c>
       <c r="F17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G17" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="18">
@@ -1013,10 +1013,10 @@
         <v>PASS</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G18" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="19">
@@ -1039,7 +1039,7 @@
         <v>7</v>
       </c>
       <c r="G19" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="20">
@@ -1059,10 +1059,10 @@
         <v>PASS</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G20" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="21">
@@ -1082,10 +1082,10 @@
         <v>PASS</v>
       </c>
       <c r="F21">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G21" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="22">
@@ -1108,7 +1108,7 @@
         <v>8</v>
       </c>
       <c r="G22" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="23">
@@ -1128,10 +1128,10 @@
         <v>PASS</v>
       </c>
       <c r="F23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G23" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="24">
@@ -1151,10 +1151,10 @@
         <v>PASS</v>
       </c>
       <c r="F24">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G24" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="25">
@@ -1174,10 +1174,10 @@
         <v>PASS</v>
       </c>
       <c r="F25">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G25" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="26">
@@ -1197,10 +1197,10 @@
         <v>PASS</v>
       </c>
       <c r="F26">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G26" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="27">
@@ -1220,10 +1220,10 @@
         <v>PASS</v>
       </c>
       <c r="F27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="28">
@@ -1243,10 +1243,10 @@
         <v>PASS</v>
       </c>
       <c r="F28">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G28" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="29">
@@ -1266,10 +1266,10 @@
         <v>PASS</v>
       </c>
       <c r="F29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G29" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="30">
@@ -1289,10 +1289,10 @@
         <v>PASS</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G30" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="31">
@@ -1312,10 +1312,10 @@
         <v>PASS</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G31" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="32">
@@ -1335,10 +1335,10 @@
         <v>PASS</v>
       </c>
       <c r="F32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G32" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="33">
@@ -1358,10 +1358,10 @@
         <v>PASS</v>
       </c>
       <c r="F33">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G33" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="34">
@@ -1384,7 +1384,7 @@
         <v>3</v>
       </c>
       <c r="G34" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="35">
@@ -1404,10 +1404,10 @@
         <v>PASS</v>
       </c>
       <c r="F35">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G35" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="36">
@@ -1427,10 +1427,10 @@
         <v>PASS</v>
       </c>
       <c r="F36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G36" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="37">
@@ -1450,10 +1450,10 @@
         <v>PASS</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G37" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="38">
@@ -1473,10 +1473,10 @@
         <v>PASS</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G38" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="39">
@@ -1496,10 +1496,10 @@
         <v>PASS</v>
       </c>
       <c r="F39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G39" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="40">
@@ -1519,10 +1519,10 @@
         <v>PASS</v>
       </c>
       <c r="F40">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G40" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="41">
@@ -1542,10 +1542,10 @@
         <v>PASS</v>
       </c>
       <c r="F41">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G41" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="42">
@@ -1565,10 +1565,10 @@
         <v>PASS</v>
       </c>
       <c r="F42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G42" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="43">
@@ -1588,10 +1588,10 @@
         <v>PASS</v>
       </c>
       <c r="F43">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G43" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="44">
@@ -1611,10 +1611,10 @@
         <v>PASS</v>
       </c>
       <c r="F44">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G44" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="45">
@@ -1634,10 +1634,10 @@
         <v>PASS</v>
       </c>
       <c r="F45">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G45" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="46">
@@ -1657,10 +1657,10 @@
         <v>PASS</v>
       </c>
       <c r="F46">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G46" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="47">
@@ -1680,10 +1680,10 @@
         <v>PASS</v>
       </c>
       <c r="F47">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G47" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="48">
@@ -1703,10 +1703,10 @@
         <v>PASS</v>
       </c>
       <c r="F48">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G48" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="49">
@@ -1726,10 +1726,10 @@
         <v>PASS</v>
       </c>
       <c r="F49">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G49" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="50">
@@ -1749,10 +1749,10 @@
         <v>PASS</v>
       </c>
       <c r="F50">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G50" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="51">
@@ -1775,7 +1775,7 @@
         <v>3</v>
       </c>
       <c r="G51" t="str">
-        <v>2026-08-06T04:13:19.081Z</v>
+        <v>2026-08-06T04:28:12.192Z</v>
       </c>
     </row>
     <row r="52">
@@ -1795,10 +1795,10 @@
         <v>PASS</v>
       </c>
       <c r="F52">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G52" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.195Z</v>
       </c>
     </row>
     <row r="53">
@@ -1818,10 +1818,10 @@
         <v>PASS</v>
       </c>
       <c r="F53">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G53" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.195Z</v>
       </c>
     </row>
     <row r="54">
@@ -1841,10 +1841,10 @@
         <v>PASS</v>
       </c>
       <c r="F54">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G54" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.195Z</v>
       </c>
     </row>
     <row r="55">
@@ -1864,10 +1864,10 @@
         <v>PASS</v>
       </c>
       <c r="F55">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G55" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.195Z</v>
       </c>
     </row>
     <row r="56">
@@ -1887,10 +1887,10 @@
         <v>PASS</v>
       </c>
       <c r="F56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G56" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.195Z</v>
       </c>
     </row>
     <row r="57">
@@ -1910,10 +1910,10 @@
         <v>PASS</v>
       </c>
       <c r="F57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G57" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.195Z</v>
       </c>
     </row>
     <row r="58">
@@ -1933,10 +1933,10 @@
         <v>PASS</v>
       </c>
       <c r="F58">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G58" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.195Z</v>
       </c>
     </row>
     <row r="59">
@@ -1956,10 +1956,10 @@
         <v>PASS</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G59" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.195Z</v>
       </c>
     </row>
     <row r="60">
@@ -1979,10 +1979,10 @@
         <v>PASS</v>
       </c>
       <c r="F60">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G60" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.195Z</v>
       </c>
     </row>
     <row r="61">
@@ -2005,7 +2005,7 @@
         <v>7</v>
       </c>
       <c r="G61" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.195Z</v>
       </c>
     </row>
     <row r="62">
@@ -2025,10 +2025,10 @@
         <v>PASS</v>
       </c>
       <c r="F62">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G62" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.195Z</v>
       </c>
     </row>
     <row r="63">
@@ -2048,10 +2048,10 @@
         <v>PASS</v>
       </c>
       <c r="F63">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G63" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.195Z</v>
       </c>
     </row>
     <row r="64">
@@ -2074,7 +2074,7 @@
         <v>5</v>
       </c>
       <c r="G64" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.195Z</v>
       </c>
     </row>
     <row r="65">
@@ -2094,10 +2094,10 @@
         <v>PASS</v>
       </c>
       <c r="F65">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G65" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.195Z</v>
       </c>
     </row>
     <row r="66">
@@ -2117,10 +2117,10 @@
         <v>PASS</v>
       </c>
       <c r="F66">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G66" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.195Z</v>
       </c>
     </row>
     <row r="67">
@@ -2140,10 +2140,10 @@
         <v>PASS</v>
       </c>
       <c r="F67">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G67" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="68">
@@ -2163,10 +2163,10 @@
         <v>PASS</v>
       </c>
       <c r="F68">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G68" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="69">
@@ -2186,10 +2186,10 @@
         <v>PASS</v>
       </c>
       <c r="F69">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G69" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="70">
@@ -2209,10 +2209,10 @@
         <v>PASS</v>
       </c>
       <c r="F70">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G70" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="71">
@@ -2232,10 +2232,10 @@
         <v>PASS</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G71" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="72">
@@ -2258,7 +2258,7 @@
         <v>2</v>
       </c>
       <c r="G72" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="73">
@@ -2278,10 +2278,10 @@
         <v>PASS</v>
       </c>
       <c r="F73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G73" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="74">
@@ -2301,10 +2301,10 @@
         <v>PASS</v>
       </c>
       <c r="F74">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G74" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="75">
@@ -2324,10 +2324,10 @@
         <v>PASS</v>
       </c>
       <c r="F75">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G75" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="76">
@@ -2350,7 +2350,7 @@
         <v>3</v>
       </c>
       <c r="G76" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="77">
@@ -2373,7 +2373,7 @@
         <v>5</v>
       </c>
       <c r="G77" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="78">
@@ -2393,10 +2393,10 @@
         <v>PASS</v>
       </c>
       <c r="F78">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G78" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="79">
@@ -2419,7 +2419,7 @@
         <v>4</v>
       </c>
       <c r="G79" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="80">
@@ -2439,10 +2439,10 @@
         <v>PASS</v>
       </c>
       <c r="F80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G80" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="81">
@@ -2462,10 +2462,10 @@
         <v>PASS</v>
       </c>
       <c r="F81">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G81" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="82">
@@ -2485,10 +2485,10 @@
         <v>PASS</v>
       </c>
       <c r="F82">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G82" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="83">
@@ -2508,10 +2508,10 @@
         <v>PASS</v>
       </c>
       <c r="F83">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G83" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="84">
@@ -2531,10 +2531,10 @@
         <v>PASS</v>
       </c>
       <c r="F84">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G84" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="85">
@@ -2554,10 +2554,10 @@
         <v>PASS</v>
       </c>
       <c r="F85">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G85" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="86">
@@ -2577,10 +2577,10 @@
         <v>PASS</v>
       </c>
       <c r="F86">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G86" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="87">
@@ -2600,10 +2600,10 @@
         <v>PASS</v>
       </c>
       <c r="F87">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G87" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="88">
@@ -2623,10 +2623,10 @@
         <v>PASS</v>
       </c>
       <c r="F88">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G88" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="89">
@@ -2646,10 +2646,10 @@
         <v>PASS</v>
       </c>
       <c r="F89">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G89" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="90">
@@ -2669,10 +2669,10 @@
         <v>PASS</v>
       </c>
       <c r="F90">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G90" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="91">
@@ -2692,10 +2692,10 @@
         <v>PASS</v>
       </c>
       <c r="F91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G91" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="92">
@@ -2715,10 +2715,10 @@
         <v>PASS</v>
       </c>
       <c r="F92">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G92" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="93">
@@ -2738,10 +2738,10 @@
         <v>PASS</v>
       </c>
       <c r="F93">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G93" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="94">
@@ -2761,10 +2761,10 @@
         <v>PASS</v>
       </c>
       <c r="F94">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G94" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="95">
@@ -2784,10 +2784,10 @@
         <v>PASS</v>
       </c>
       <c r="F95">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G95" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="96">
@@ -2807,10 +2807,10 @@
         <v>PASS</v>
       </c>
       <c r="F96">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G96" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="97">
@@ -2830,10 +2830,10 @@
         <v>PASS</v>
       </c>
       <c r="F97">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G97" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="98">
@@ -2856,7 +2856,7 @@
         <v>3</v>
       </c>
       <c r="G98" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="99">
@@ -2876,10 +2876,10 @@
         <v>PASS</v>
       </c>
       <c r="F99">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G99" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="100">
@@ -2893,16 +2893,16 @@
         <v>02_diagnostic_engine.test.js</v>
       </c>
       <c r="D100" t="str">
-        <v>UNIT-099: Symptom Duration Unit Converter (Hours-&gt;Days)</v>
+        <v>UNIT-099: Symptom Duration Unit Converter (Hours to Days)</v>
       </c>
       <c r="E100" t="str">
         <v>PASS</v>
       </c>
       <c r="F100">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G100" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="101">
@@ -2922,10 +2922,10 @@
         <v>PASS</v>
       </c>
       <c r="F101">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G101" t="str">
-        <v>2026-08-06T04:13:19.095Z</v>
+        <v>2026-08-06T04:28:12.196Z</v>
       </c>
     </row>
     <row r="102">
@@ -2945,10 +2945,10 @@
         <v>PASS</v>
       </c>
       <c r="F102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G102" t="str">
-        <v>2026-08-06T04:13:19.107Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="103">
@@ -2968,10 +2968,10 @@
         <v>PASS</v>
       </c>
       <c r="F103">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G103" t="str">
-        <v>2026-08-06T04:13:19.107Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="104">
@@ -2991,10 +2991,10 @@
         <v>PASS</v>
       </c>
       <c r="F104">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G104" t="str">
-        <v>2026-08-06T04:13:19.107Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="105">
@@ -3014,10 +3014,10 @@
         <v>PASS</v>
       </c>
       <c r="F105">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G105" t="str">
-        <v>2026-08-06T04:13:19.107Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="106">
@@ -3037,10 +3037,10 @@
         <v>PASS</v>
       </c>
       <c r="F106">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G106" t="str">
-        <v>2026-08-06T04:13:19.107Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="107">
@@ -3060,10 +3060,10 @@
         <v>PASS</v>
       </c>
       <c r="F107">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G107" t="str">
-        <v>2026-08-06T04:13:19.107Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="108">
@@ -3083,10 +3083,10 @@
         <v>PASS</v>
       </c>
       <c r="F108">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G108" t="str">
-        <v>2026-08-06T04:13:19.107Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="109">
@@ -3109,7 +3109,7 @@
         <v>6</v>
       </c>
       <c r="G109" t="str">
-        <v>2026-08-06T04:13:19.107Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="110">
@@ -3129,10 +3129,10 @@
         <v>PASS</v>
       </c>
       <c r="F110">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G110" t="str">
-        <v>2026-08-06T04:13:19.107Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="111">
@@ -3152,10 +3152,10 @@
         <v>PASS</v>
       </c>
       <c r="F111">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G111" t="str">
-        <v>2026-08-06T04:13:19.107Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="112">
@@ -3175,10 +3175,10 @@
         <v>PASS</v>
       </c>
       <c r="F112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G112" t="str">
-        <v>2026-08-06T04:13:19.107Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="113">
@@ -3198,10 +3198,10 @@
         <v>PASS</v>
       </c>
       <c r="F113">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G113" t="str">
-        <v>2026-08-06T04:13:19.107Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="114">
@@ -3221,10 +3221,10 @@
         <v>PASS</v>
       </c>
       <c r="F114">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G114" t="str">
-        <v>2026-08-06T04:13:19.107Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="115">
@@ -3244,10 +3244,10 @@
         <v>PASS</v>
       </c>
       <c r="F115">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G115" t="str">
-        <v>2026-08-06T04:13:19.107Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="116">
@@ -3267,10 +3267,10 @@
         <v>PASS</v>
       </c>
       <c r="F116">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G116" t="str">
-        <v>2026-08-06T04:13:19.107Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="117">
@@ -3290,10 +3290,10 @@
         <v>PASS</v>
       </c>
       <c r="F117">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G117" t="str">
-        <v>2026-08-06T04:13:19.107Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="118">
@@ -3316,7 +3316,7 @@
         <v>8</v>
       </c>
       <c r="G118" t="str">
-        <v>2026-08-06T04:13:19.107Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="119">
@@ -3336,10 +3336,10 @@
         <v>PASS</v>
       </c>
       <c r="F119">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G119" t="str">
-        <v>2026-08-06T04:13:19.107Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="120">
@@ -3359,10 +3359,10 @@
         <v>PASS</v>
       </c>
       <c r="F120">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G120" t="str">
-        <v>2026-08-06T04:13:19.107Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="121">
@@ -3382,10 +3382,10 @@
         <v>PASS</v>
       </c>
       <c r="F121">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G121" t="str">
-        <v>2026-08-06T04:13:19.107Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="122">
@@ -3405,10 +3405,10 @@
         <v>PASS</v>
       </c>
       <c r="F122">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G122" t="str">
-        <v>2026-08-06T04:13:19.107Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="123">
@@ -3428,10 +3428,10 @@
         <v>PASS</v>
       </c>
       <c r="F123">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G123" t="str">
-        <v>2026-08-06T04:13:19.107Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="124">
@@ -3454,7 +3454,7 @@
         <v>7</v>
       </c>
       <c r="G124" t="str">
-        <v>2026-08-06T04:13:19.108Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="125">
@@ -3474,10 +3474,10 @@
         <v>PASS</v>
       </c>
       <c r="F125">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G125" t="str">
-        <v>2026-08-06T04:13:19.108Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="126">
@@ -3500,7 +3500,7 @@
         <v>8</v>
       </c>
       <c r="G126" t="str">
-        <v>2026-08-06T04:13:19.108Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="127">
@@ -3520,10 +3520,10 @@
         <v>PASS</v>
       </c>
       <c r="F127">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G127" t="str">
-        <v>2026-08-06T04:13:19.108Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="128">
@@ -3543,10 +3543,10 @@
         <v>PASS</v>
       </c>
       <c r="F128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G128" t="str">
-        <v>2026-08-06T04:13:19.108Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="129">
@@ -3566,10 +3566,10 @@
         <v>PASS</v>
       </c>
       <c r="F129">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G129" t="str">
-        <v>2026-08-06T04:13:19.108Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="130">
@@ -3589,10 +3589,10 @@
         <v>PASS</v>
       </c>
       <c r="F130">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G130" t="str">
-        <v>2026-08-06T04:13:19.108Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="131">
@@ -3612,10 +3612,10 @@
         <v>PASS</v>
       </c>
       <c r="F131">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G131" t="str">
-        <v>2026-08-06T04:13:19.108Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="132">
@@ -3638,7 +3638,7 @@
         <v>3</v>
       </c>
       <c r="G132" t="str">
-        <v>2026-08-06T04:13:19.108Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="133">
@@ -3658,10 +3658,10 @@
         <v>PASS</v>
       </c>
       <c r="F133">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G133" t="str">
-        <v>2026-08-06T04:13:19.108Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="134">
@@ -3681,10 +3681,10 @@
         <v>PASS</v>
       </c>
       <c r="F134">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G134" t="str">
-        <v>2026-08-06T04:13:19.108Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="135">
@@ -3704,10 +3704,10 @@
         <v>PASS</v>
       </c>
       <c r="F135">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G135" t="str">
-        <v>2026-08-06T04:13:19.108Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="136">
@@ -3727,10 +3727,10 @@
         <v>PASS</v>
       </c>
       <c r="F136">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G136" t="str">
-        <v>2026-08-06T04:13:19.108Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="137">
@@ -3750,10 +3750,10 @@
         <v>PASS</v>
       </c>
       <c r="F137">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G137" t="str">
-        <v>2026-08-06T04:13:19.108Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="138">
@@ -3773,10 +3773,10 @@
         <v>PASS</v>
       </c>
       <c r="F138">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G138" t="str">
-        <v>2026-08-06T04:13:19.108Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="139">
@@ -3799,7 +3799,7 @@
         <v>5</v>
       </c>
       <c r="G139" t="str">
-        <v>2026-08-06T04:13:19.108Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="140">
@@ -3822,7 +3822,7 @@
         <v>7</v>
       </c>
       <c r="G140" t="str">
-        <v>2026-08-06T04:13:19.108Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="141">
@@ -3842,10 +3842,10 @@
         <v>PASS</v>
       </c>
       <c r="F141">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G141" t="str">
-        <v>2026-08-06T04:13:19.108Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="142">
@@ -3865,10 +3865,10 @@
         <v>PASS</v>
       </c>
       <c r="F142">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G142" t="str">
-        <v>2026-08-06T04:13:19.108Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="143">
@@ -3888,10 +3888,10 @@
         <v>PASS</v>
       </c>
       <c r="F143">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G143" t="str">
-        <v>2026-08-06T04:13:19.108Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="144">
@@ -3914,7 +3914,7 @@
         <v>6</v>
       </c>
       <c r="G144" t="str">
-        <v>2026-08-06T04:13:19.108Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="145">
@@ -3934,10 +3934,10 @@
         <v>PASS</v>
       </c>
       <c r="F145">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G145" t="str">
-        <v>2026-08-06T04:13:19.108Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="146">
@@ -3957,10 +3957,10 @@
         <v>PASS</v>
       </c>
       <c r="F146">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G146" t="str">
-        <v>2026-08-06T04:13:19.108Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="147">
@@ -3980,10 +3980,10 @@
         <v>PASS</v>
       </c>
       <c r="F147">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G147" t="str">
-        <v>2026-08-06T04:13:19.108Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="148">
@@ -4003,10 +4003,10 @@
         <v>PASS</v>
       </c>
       <c r="F148">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G148" t="str">
-        <v>2026-08-06T04:13:19.108Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="149">
@@ -4026,10 +4026,10 @@
         <v>PASS</v>
       </c>
       <c r="F149">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G149" t="str">
-        <v>2026-08-06T04:13:19.108Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="150">
@@ -4052,7 +4052,7 @@
         <v>6</v>
       </c>
       <c r="G150" t="str">
-        <v>2026-08-06T04:13:19.108Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="151">
@@ -4072,10 +4072,10 @@
         <v>PASS</v>
       </c>
       <c r="F151">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G151" t="str">
-        <v>2026-08-06T04:13:19.108Z</v>
+        <v>2026-08-06T04:28:12.199Z</v>
       </c>
     </row>
     <row r="152">
@@ -4095,10 +4095,10 @@
         <v>PASS</v>
       </c>
       <c r="F152">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G152" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="153">
@@ -4118,10 +4118,10 @@
         <v>PASS</v>
       </c>
       <c r="F153">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G153" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="154">
@@ -4141,10 +4141,10 @@
         <v>PASS</v>
       </c>
       <c r="F154">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G154" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="155">
@@ -4164,10 +4164,10 @@
         <v>PASS</v>
       </c>
       <c r="F155">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G155" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="156">
@@ -4187,10 +4187,10 @@
         <v>PASS</v>
       </c>
       <c r="F156">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G156" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="157">
@@ -4210,10 +4210,10 @@
         <v>PASS</v>
       </c>
       <c r="F157">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G157" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="158">
@@ -4233,10 +4233,10 @@
         <v>PASS</v>
       </c>
       <c r="F158">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G158" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="159">
@@ -4256,10 +4256,10 @@
         <v>PASS</v>
       </c>
       <c r="F159">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G159" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="160">
@@ -4279,10 +4279,10 @@
         <v>PASS</v>
       </c>
       <c r="F160">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G160" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="161">
@@ -4302,10 +4302,10 @@
         <v>PASS</v>
       </c>
       <c r="F161">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G161" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="162">
@@ -4325,10 +4325,10 @@
         <v>PASS</v>
       </c>
       <c r="F162">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G162" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="163">
@@ -4348,10 +4348,10 @@
         <v>PASS</v>
       </c>
       <c r="F163">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G163" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="164">
@@ -4374,7 +4374,7 @@
         <v>7</v>
       </c>
       <c r="G164" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="165">
@@ -4394,10 +4394,10 @@
         <v>PASS</v>
       </c>
       <c r="F165">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G165" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="166">
@@ -4417,10 +4417,10 @@
         <v>PASS</v>
       </c>
       <c r="F166">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G166" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="167">
@@ -4440,10 +4440,10 @@
         <v>PASS</v>
       </c>
       <c r="F167">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G167" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="168">
@@ -4466,7 +4466,7 @@
         <v>8</v>
       </c>
       <c r="G168" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="169">
@@ -4486,10 +4486,10 @@
         <v>PASS</v>
       </c>
       <c r="F169">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G169" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="170">
@@ -4509,10 +4509,10 @@
         <v>PASS</v>
       </c>
       <c r="F170">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G170" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="171">
@@ -4532,10 +4532,10 @@
         <v>PASS</v>
       </c>
       <c r="F171">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G171" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="172">
@@ -4555,10 +4555,10 @@
         <v>PASS</v>
       </c>
       <c r="F172">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G172" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="173">
@@ -4578,10 +4578,10 @@
         <v>PASS</v>
       </c>
       <c r="F173">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G173" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="174">
@@ -4601,10 +4601,10 @@
         <v>PASS</v>
       </c>
       <c r="F174">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G174" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="175">
@@ -4627,7 +4627,7 @@
         <v>5</v>
       </c>
       <c r="G175" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="176">
@@ -4647,10 +4647,10 @@
         <v>PASS</v>
       </c>
       <c r="F176">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G176" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="177">
@@ -4670,10 +4670,10 @@
         <v>PASS</v>
       </c>
       <c r="F177">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G177" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="178">
@@ -4693,10 +4693,10 @@
         <v>PASS</v>
       </c>
       <c r="F178">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G178" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="179">
@@ -4716,10 +4716,10 @@
         <v>PASS</v>
       </c>
       <c r="F179">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G179" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="180">
@@ -4739,10 +4739,10 @@
         <v>PASS</v>
       </c>
       <c r="F180">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G180" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="181">
@@ -4762,10 +4762,10 @@
         <v>PASS</v>
       </c>
       <c r="F181">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G181" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="182">
@@ -4785,10 +4785,10 @@
         <v>PASS</v>
       </c>
       <c r="F182">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G182" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="183">
@@ -4808,10 +4808,10 @@
         <v>PASS</v>
       </c>
       <c r="F183">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G183" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="184">
@@ -4831,10 +4831,10 @@
         <v>PASS</v>
       </c>
       <c r="F184">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G184" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="185">
@@ -4854,10 +4854,10 @@
         <v>PASS</v>
       </c>
       <c r="F185">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G185" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="186">
@@ -4877,10 +4877,10 @@
         <v>PASS</v>
       </c>
       <c r="F186">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G186" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="187">
@@ -4900,10 +4900,10 @@
         <v>PASS</v>
       </c>
       <c r="F187">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G187" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="188">
@@ -4923,10 +4923,10 @@
         <v>PASS</v>
       </c>
       <c r="F188">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G188" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="189">
@@ -4946,10 +4946,10 @@
         <v>PASS</v>
       </c>
       <c r="F189">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G189" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="190">
@@ -4969,10 +4969,10 @@
         <v>PASS</v>
       </c>
       <c r="F190">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G190" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="191">
@@ -4992,10 +4992,10 @@
         <v>PASS</v>
       </c>
       <c r="F191">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G191" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="192">
@@ -5015,10 +5015,10 @@
         <v>PASS</v>
       </c>
       <c r="F192">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G192" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="193">
@@ -5038,10 +5038,10 @@
         <v>PASS</v>
       </c>
       <c r="F193">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G193" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="194">
@@ -5061,10 +5061,10 @@
         <v>PASS</v>
       </c>
       <c r="F194">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G194" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="195">
@@ -5084,10 +5084,10 @@
         <v>PASS</v>
       </c>
       <c r="F195">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G195" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="196">
@@ -5107,10 +5107,10 @@
         <v>PASS</v>
       </c>
       <c r="F196">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G196" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="197">
@@ -5130,10 +5130,10 @@
         <v>PASS</v>
       </c>
       <c r="F197">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G197" t="str">
-        <v>2026-08-06T04:13:19.120Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="198">
@@ -5153,10 +5153,10 @@
         <v>PASS</v>
       </c>
       <c r="F198">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G198" t="str">
-        <v>2026-08-06T04:13:19.121Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="199">
@@ -5176,10 +5176,10 @@
         <v>PASS</v>
       </c>
       <c r="F199">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G199" t="str">
-        <v>2026-08-06T04:13:19.121Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="200">
@@ -5199,10 +5199,10 @@
         <v>PASS</v>
       </c>
       <c r="F200">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G200" t="str">
-        <v>2026-08-06T04:13:19.121Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="201">
@@ -5222,10 +5222,10 @@
         <v>PASS</v>
       </c>
       <c r="F201">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G201" t="str">
-        <v>2026-08-06T04:13:19.121Z</v>
+        <v>2026-08-06T04:28:12.201Z</v>
       </c>
     </row>
     <row r="202">
@@ -5245,10 +5245,10 @@
         <v>PASS</v>
       </c>
       <c r="F202">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G202" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="203">
@@ -5271,7 +5271,7 @@
         <v>3</v>
       </c>
       <c r="G203" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="204">
@@ -5291,10 +5291,10 @@
         <v>PASS</v>
       </c>
       <c r="F204">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G204" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="205">
@@ -5314,10 +5314,10 @@
         <v>PASS</v>
       </c>
       <c r="F205">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G205" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="206">
@@ -5337,10 +5337,10 @@
         <v>PASS</v>
       </c>
       <c r="F206">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G206" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="207">
@@ -5363,7 +5363,7 @@
         <v>1</v>
       </c>
       <c r="G207" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="208">
@@ -5383,10 +5383,10 @@
         <v>PASS</v>
       </c>
       <c r="F208">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G208" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="209">
@@ -5406,10 +5406,10 @@
         <v>PASS</v>
       </c>
       <c r="F209">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G209" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="210">
@@ -5432,7 +5432,7 @@
         <v>1</v>
       </c>
       <c r="G210" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="211">
@@ -5452,10 +5452,10 @@
         <v>PASS</v>
       </c>
       <c r="F211">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G211" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="212">
@@ -5478,7 +5478,7 @@
         <v>1</v>
       </c>
       <c r="G212" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="213">
@@ -5498,10 +5498,10 @@
         <v>PASS</v>
       </c>
       <c r="F213">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G213" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="214">
@@ -5521,10 +5521,10 @@
         <v>PASS</v>
       </c>
       <c r="F214">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G214" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="215">
@@ -5544,10 +5544,10 @@
         <v>PASS</v>
       </c>
       <c r="F215">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G215" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="216">
@@ -5567,10 +5567,10 @@
         <v>PASS</v>
       </c>
       <c r="F216">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G216" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="217">
@@ -5590,10 +5590,10 @@
         <v>PASS</v>
       </c>
       <c r="F217">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G217" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="218">
@@ -5613,10 +5613,10 @@
         <v>PASS</v>
       </c>
       <c r="F218">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G218" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="219">
@@ -5636,10 +5636,10 @@
         <v>PASS</v>
       </c>
       <c r="F219">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G219" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="220">
@@ -5659,10 +5659,10 @@
         <v>PASS</v>
       </c>
       <c r="F220">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G220" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="221">
@@ -5682,10 +5682,10 @@
         <v>PASS</v>
       </c>
       <c r="F221">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G221" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="222">
@@ -5705,10 +5705,10 @@
         <v>PASS</v>
       </c>
       <c r="F222">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G222" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="223">
@@ -5728,10 +5728,10 @@
         <v>PASS</v>
       </c>
       <c r="F223">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G223" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="224">
@@ -5751,10 +5751,10 @@
         <v>PASS</v>
       </c>
       <c r="F224">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G224" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="225">
@@ -5777,7 +5777,7 @@
         <v>2</v>
       </c>
       <c r="G225" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="226">
@@ -5797,10 +5797,10 @@
         <v>PASS</v>
       </c>
       <c r="F226">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G226" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="227">
@@ -5820,10 +5820,10 @@
         <v>PASS</v>
       </c>
       <c r="F227">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G227" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="228">
@@ -5843,10 +5843,10 @@
         <v>PASS</v>
       </c>
       <c r="F228">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G228" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="229">
@@ -5869,7 +5869,7 @@
         <v>7</v>
       </c>
       <c r="G229" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="230">
@@ -5889,10 +5889,10 @@
         <v>PASS</v>
       </c>
       <c r="F230">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G230" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="231">
@@ -5912,10 +5912,10 @@
         <v>PASS</v>
       </c>
       <c r="F231">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G231" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="232">
@@ -5935,10 +5935,10 @@
         <v>PASS</v>
       </c>
       <c r="F232">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G232" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="233">
@@ -5958,10 +5958,10 @@
         <v>PASS</v>
       </c>
       <c r="F233">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G233" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="234">
@@ -5984,7 +5984,7 @@
         <v>3</v>
       </c>
       <c r="G234" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="235">
@@ -6004,10 +6004,10 @@
         <v>PASS</v>
       </c>
       <c r="F235">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G235" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="236">
@@ -6027,10 +6027,10 @@
         <v>PASS</v>
       </c>
       <c r="F236">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G236" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="237">
@@ -6050,10 +6050,10 @@
         <v>PASS</v>
       </c>
       <c r="F237">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G237" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="238">
@@ -6073,10 +6073,10 @@
         <v>PASS</v>
       </c>
       <c r="F238">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G238" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="239">
@@ -6096,10 +6096,10 @@
         <v>PASS</v>
       </c>
       <c r="F239">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G239" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="240">
@@ -6119,10 +6119,10 @@
         <v>PASS</v>
       </c>
       <c r="F240">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G240" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="241">
@@ -6142,10 +6142,10 @@
         <v>PASS</v>
       </c>
       <c r="F241">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G241" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="242">
@@ -6165,10 +6165,10 @@
         <v>PASS</v>
       </c>
       <c r="F242">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G242" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="243">
@@ -6188,10 +6188,10 @@
         <v>PASS</v>
       </c>
       <c r="F243">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G243" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="244">
@@ -6211,10 +6211,10 @@
         <v>PASS</v>
       </c>
       <c r="F244">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G244" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="245">
@@ -6234,10 +6234,10 @@
         <v>PASS</v>
       </c>
       <c r="F245">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G245" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="246">
@@ -6257,10 +6257,10 @@
         <v>PASS</v>
       </c>
       <c r="F246">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G246" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="247">
@@ -6280,10 +6280,10 @@
         <v>PASS</v>
       </c>
       <c r="F247">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G247" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="248">
@@ -6303,10 +6303,10 @@
         <v>PASS</v>
       </c>
       <c r="F248">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G248" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="249">
@@ -6326,10 +6326,10 @@
         <v>PASS</v>
       </c>
       <c r="F249">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G249" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="250">
@@ -6349,10 +6349,10 @@
         <v>PASS</v>
       </c>
       <c r="F250">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G250" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="251">
@@ -6375,7 +6375,7 @@
         <v>2</v>
       </c>
       <c r="G251" t="str">
-        <v>2026-08-06T04:13:19.141Z</v>
+        <v>2026-08-06T04:28:12.203Z</v>
       </c>
     </row>
     <row r="252">
@@ -6395,10 +6395,10 @@
         <v>PASS</v>
       </c>
       <c r="F252">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G252" t="str">
-        <v>2026-08-06T04:13:19.152Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="253">
@@ -6418,10 +6418,10 @@
         <v>PASS</v>
       </c>
       <c r="F253">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G253" t="str">
-        <v>2026-08-06T04:13:19.152Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="254">
@@ -6444,7 +6444,7 @@
         <v>2</v>
       </c>
       <c r="G254" t="str">
-        <v>2026-08-06T04:13:19.152Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="255">
@@ -6464,10 +6464,10 @@
         <v>PASS</v>
       </c>
       <c r="F255">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G255" t="str">
-        <v>2026-08-06T04:13:19.152Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="256">
@@ -6487,10 +6487,10 @@
         <v>PASS</v>
       </c>
       <c r="F256">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G256" t="str">
-        <v>2026-08-06T04:13:19.152Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="257">
@@ -6510,10 +6510,10 @@
         <v>PASS</v>
       </c>
       <c r="F257">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G257" t="str">
-        <v>2026-08-06T04:13:19.152Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="258">
@@ -6533,10 +6533,10 @@
         <v>PASS</v>
       </c>
       <c r="F258">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G258" t="str">
-        <v>2026-08-06T04:13:19.152Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="259">
@@ -6556,10 +6556,10 @@
         <v>PASS</v>
       </c>
       <c r="F259">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G259" t="str">
-        <v>2026-08-06T04:13:19.152Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="260">
@@ -6582,7 +6582,7 @@
         <v>1</v>
       </c>
       <c r="G260" t="str">
-        <v>2026-08-06T04:13:19.152Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="261">
@@ -6602,10 +6602,10 @@
         <v>PASS</v>
       </c>
       <c r="F261">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G261" t="str">
-        <v>2026-08-06T04:13:19.152Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="262">
@@ -6625,10 +6625,10 @@
         <v>PASS</v>
       </c>
       <c r="F262">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G262" t="str">
-        <v>2026-08-06T04:13:19.152Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="263">
@@ -6648,10 +6648,10 @@
         <v>PASS</v>
       </c>
       <c r="F263">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G263" t="str">
-        <v>2026-08-06T04:13:19.152Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="264">
@@ -6671,10 +6671,10 @@
         <v>PASS</v>
       </c>
       <c r="F264">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G264" t="str">
-        <v>2026-08-06T04:13:19.152Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="265">
@@ -6697,7 +6697,7 @@
         <v>1</v>
       </c>
       <c r="G265" t="str">
-        <v>2026-08-06T04:13:19.152Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="266">
@@ -6717,10 +6717,10 @@
         <v>PASS</v>
       </c>
       <c r="F266">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G266" t="str">
-        <v>2026-08-06T04:13:19.152Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="267">
@@ -6743,7 +6743,7 @@
         <v>6</v>
       </c>
       <c r="G267" t="str">
-        <v>2026-08-06T04:13:19.152Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="268">
@@ -6763,10 +6763,10 @@
         <v>PASS</v>
       </c>
       <c r="F268">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G268" t="str">
-        <v>2026-08-06T04:13:19.152Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="269">
@@ -6786,10 +6786,10 @@
         <v>PASS</v>
       </c>
       <c r="F269">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G269" t="str">
-        <v>2026-08-06T04:13:19.152Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="270">
@@ -6809,10 +6809,10 @@
         <v>PASS</v>
       </c>
       <c r="F270">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G270" t="str">
-        <v>2026-08-06T04:13:19.152Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="271">
@@ -6832,10 +6832,10 @@
         <v>PASS</v>
       </c>
       <c r="F271">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G271" t="str">
-        <v>2026-08-06T04:13:19.152Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="272">
@@ -6855,10 +6855,10 @@
         <v>PASS</v>
       </c>
       <c r="F272">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G272" t="str">
-        <v>2026-08-06T04:13:19.152Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="273">
@@ -6878,10 +6878,10 @@
         <v>PASS</v>
       </c>
       <c r="F273">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G273" t="str">
-        <v>2026-08-06T04:13:19.152Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="274">
@@ -6901,10 +6901,10 @@
         <v>PASS</v>
       </c>
       <c r="F274">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G274" t="str">
-        <v>2026-08-06T04:13:19.152Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="275">
@@ -6924,10 +6924,10 @@
         <v>PASS</v>
       </c>
       <c r="F275">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G275" t="str">
-        <v>2026-08-06T04:13:19.152Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="276">
@@ -6947,10 +6947,10 @@
         <v>PASS</v>
       </c>
       <c r="F276">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G276" t="str">
-        <v>2026-08-06T04:13:19.152Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="277">
@@ -6973,7 +6973,7 @@
         <v>4</v>
       </c>
       <c r="G277" t="str">
-        <v>2026-08-06T04:13:19.152Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="278">
@@ -6993,10 +6993,10 @@
         <v>PASS</v>
       </c>
       <c r="F278">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G278" t="str">
-        <v>2026-08-06T04:13:19.152Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="279">
@@ -7016,10 +7016,10 @@
         <v>PASS</v>
       </c>
       <c r="F279">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G279" t="str">
-        <v>2026-08-06T04:13:19.153Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="280">
@@ -7039,10 +7039,10 @@
         <v>PASS</v>
       </c>
       <c r="F280">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G280" t="str">
-        <v>2026-08-06T04:13:19.153Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="281">
@@ -7062,10 +7062,10 @@
         <v>PASS</v>
       </c>
       <c r="F281">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G281" t="str">
-        <v>2026-08-06T04:13:19.153Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="282">
@@ -7088,7 +7088,7 @@
         <v>4</v>
       </c>
       <c r="G282" t="str">
-        <v>2026-08-06T04:13:19.153Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="283">
@@ -7108,10 +7108,10 @@
         <v>PASS</v>
       </c>
       <c r="F283">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G283" t="str">
-        <v>2026-08-06T04:13:19.153Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="284">
@@ -7131,10 +7131,10 @@
         <v>PASS</v>
       </c>
       <c r="F284">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G284" t="str">
-        <v>2026-08-06T04:13:19.153Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="285">
@@ -7154,10 +7154,10 @@
         <v>PASS</v>
       </c>
       <c r="F285">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G285" t="str">
-        <v>2026-08-06T04:13:19.153Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="286">
@@ -7177,10 +7177,10 @@
         <v>PASS</v>
       </c>
       <c r="F286">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G286" t="str">
-        <v>2026-08-06T04:13:19.153Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="287">
@@ -7203,7 +7203,7 @@
         <v>5</v>
       </c>
       <c r="G287" t="str">
-        <v>2026-08-06T04:13:19.153Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="288">
@@ -7223,10 +7223,10 @@
         <v>PASS</v>
       </c>
       <c r="F288">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G288" t="str">
-        <v>2026-08-06T04:13:19.153Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="289">
@@ -7249,7 +7249,7 @@
         <v>8</v>
       </c>
       <c r="G289" t="str">
-        <v>2026-08-06T04:13:19.153Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="290">
@@ -7269,10 +7269,10 @@
         <v>PASS</v>
       </c>
       <c r="F290">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G290" t="str">
-        <v>2026-08-06T04:13:19.153Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="291">
@@ -7292,10 +7292,10 @@
         <v>PASS</v>
       </c>
       <c r="F291">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G291" t="str">
-        <v>2026-08-06T04:13:19.153Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="292">
@@ -7315,10 +7315,10 @@
         <v>PASS</v>
       </c>
       <c r="F292">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G292" t="str">
-        <v>2026-08-06T04:13:19.153Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="293">
@@ -7338,10 +7338,10 @@
         <v>PASS</v>
       </c>
       <c r="F293">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G293" t="str">
-        <v>2026-08-06T04:13:19.153Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="294">
@@ -7361,10 +7361,10 @@
         <v>PASS</v>
       </c>
       <c r="F294">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G294" t="str">
-        <v>2026-08-06T04:13:19.153Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="295">
@@ -7384,10 +7384,10 @@
         <v>PASS</v>
       </c>
       <c r="F295">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G295" t="str">
-        <v>2026-08-06T04:13:19.153Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="296">
@@ -7407,10 +7407,10 @@
         <v>PASS</v>
       </c>
       <c r="F296">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G296" t="str">
-        <v>2026-08-06T04:13:19.153Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="297">
@@ -7430,10 +7430,10 @@
         <v>PASS</v>
       </c>
       <c r="F297">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G297" t="str">
-        <v>2026-08-06T04:13:19.153Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="298">
@@ -7453,10 +7453,10 @@
         <v>PASS</v>
       </c>
       <c r="F298">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G298" t="str">
-        <v>2026-08-06T04:13:19.153Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="299">
@@ -7476,10 +7476,10 @@
         <v>PASS</v>
       </c>
       <c r="F299">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G299" t="str">
-        <v>2026-08-06T04:13:19.153Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="300">
@@ -7499,10 +7499,10 @@
         <v>PASS</v>
       </c>
       <c r="F300">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G300" t="str">
-        <v>2026-08-06T04:13:19.153Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
     <row r="301">
@@ -7522,10 +7522,10 @@
         <v>PASS</v>
       </c>
       <c r="F301">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G301" t="str">
-        <v>2026-08-06T04:13:19.153Z</v>
+        <v>2026-08-06T04:28:12.206Z</v>
       </c>
     </row>
   </sheetData>

--- a/unit-tests/test-report.xlsx
+++ b/unit-tests/test-report.xlsx
@@ -442,7 +442,7 @@
         <v>Execution Timestamp</v>
       </c>
       <c r="B5" t="str">
-        <v>6/8/2026, 9:58:12 am</v>
+        <v>6/8/2026, 10:21:50 am</v>
       </c>
       <c r="C5" t="str">
         <v>Local System Time</v>
@@ -497,7 +497,7 @@
         <v>Total Suite Duration</v>
       </c>
       <c r="B10" t="str">
-        <v>0.019 seconds</v>
+        <v>0.028 seconds</v>
       </c>
       <c r="C10" t="str">
         <v>Cumulative test execution time</v>
@@ -645,10 +645,10 @@
         <v>PASS</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G2" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="3">
@@ -668,10 +668,10 @@
         <v>PASS</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G3" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="4">
@@ -691,10 +691,10 @@
         <v>PASS</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="5">
@@ -714,10 +714,10 @@
         <v>PASS</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G5" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="6">
@@ -737,10 +737,10 @@
         <v>PASS</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="7">
@@ -760,10 +760,10 @@
         <v>PASS</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G7" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="8">
@@ -783,10 +783,10 @@
         <v>PASS</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G8" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="9">
@@ -809,7 +809,7 @@
         <v>4</v>
       </c>
       <c r="G9" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="10">
@@ -829,10 +829,10 @@
         <v>PASS</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G10" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="11">
@@ -855,7 +855,7 @@
         <v>5</v>
       </c>
       <c r="G11" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="12">
@@ -875,10 +875,10 @@
         <v>PASS</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G12" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="13">
@@ -898,10 +898,10 @@
         <v>PASS</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G13" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="14">
@@ -921,10 +921,10 @@
         <v>PASS</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G14" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="15">
@@ -944,10 +944,10 @@
         <v>PASS</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="16">
@@ -967,10 +967,10 @@
         <v>PASS</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G16" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="17">
@@ -990,10 +990,10 @@
         <v>PASS</v>
       </c>
       <c r="F17">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G17" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="18">
@@ -1013,10 +1013,10 @@
         <v>PASS</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G18" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="19">
@@ -1036,10 +1036,10 @@
         <v>PASS</v>
       </c>
       <c r="F19">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G19" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="20">
@@ -1059,10 +1059,10 @@
         <v>PASS</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G20" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="21">
@@ -1082,10 +1082,10 @@
         <v>PASS</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G21" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="22">
@@ -1105,10 +1105,10 @@
         <v>PASS</v>
       </c>
       <c r="F22">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G22" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="23">
@@ -1128,10 +1128,10 @@
         <v>PASS</v>
       </c>
       <c r="F23">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G23" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="24">
@@ -1151,10 +1151,10 @@
         <v>PASS</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G24" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="25">
@@ -1174,10 +1174,10 @@
         <v>PASS</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G25" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="26">
@@ -1197,10 +1197,10 @@
         <v>PASS</v>
       </c>
       <c r="F26">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G26" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="27">
@@ -1220,10 +1220,10 @@
         <v>PASS</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="28">
@@ -1243,10 +1243,10 @@
         <v>PASS</v>
       </c>
       <c r="F28">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G28" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="29">
@@ -1266,10 +1266,10 @@
         <v>PASS</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G29" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="30">
@@ -1289,10 +1289,10 @@
         <v>PASS</v>
       </c>
       <c r="F30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G30" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="31">
@@ -1312,10 +1312,10 @@
         <v>PASS</v>
       </c>
       <c r="F31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G31" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="32">
@@ -1335,10 +1335,10 @@
         <v>PASS</v>
       </c>
       <c r="F32">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G32" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="33">
@@ -1361,7 +1361,7 @@
         <v>4</v>
       </c>
       <c r="G33" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="34">
@@ -1381,10 +1381,10 @@
         <v>PASS</v>
       </c>
       <c r="F34">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G34" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="35">
@@ -1404,10 +1404,10 @@
         <v>PASS</v>
       </c>
       <c r="F35">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G35" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="36">
@@ -1427,10 +1427,10 @@
         <v>PASS</v>
       </c>
       <c r="F36">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G36" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="37">
@@ -1450,10 +1450,10 @@
         <v>PASS</v>
       </c>
       <c r="F37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G37" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="38">
@@ -1476,7 +1476,7 @@
         <v>6</v>
       </c>
       <c r="G38" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="39">
@@ -1499,7 +1499,7 @@
         <v>1</v>
       </c>
       <c r="G39" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="40">
@@ -1519,10 +1519,10 @@
         <v>PASS</v>
       </c>
       <c r="F40">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G40" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="41">
@@ -1542,10 +1542,10 @@
         <v>PASS</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G41" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="42">
@@ -1565,10 +1565,10 @@
         <v>PASS</v>
       </c>
       <c r="F42">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G42" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="43">
@@ -1588,10 +1588,10 @@
         <v>PASS</v>
       </c>
       <c r="F43">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G43" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="44">
@@ -1611,10 +1611,10 @@
         <v>PASS</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="45">
@@ -1634,10 +1634,10 @@
         <v>PASS</v>
       </c>
       <c r="F45">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G45" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="46">
@@ -1660,7 +1660,7 @@
         <v>8</v>
       </c>
       <c r="G46" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="47">
@@ -1680,10 +1680,10 @@
         <v>PASS</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G47" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="48">
@@ -1703,10 +1703,10 @@
         <v>PASS</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G48" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="49">
@@ -1726,10 +1726,10 @@
         <v>PASS</v>
       </c>
       <c r="F49">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G49" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="50">
@@ -1749,10 +1749,10 @@
         <v>PASS</v>
       </c>
       <c r="F50">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G50" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="51">
@@ -1772,10 +1772,10 @@
         <v>PASS</v>
       </c>
       <c r="F51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G51" t="str">
-        <v>2026-08-06T04:28:12.192Z</v>
+        <v>2026-08-06T04:51:50.897Z</v>
       </c>
     </row>
     <row r="52">
@@ -1795,10 +1795,10 @@
         <v>PASS</v>
       </c>
       <c r="F52">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G52" t="str">
-        <v>2026-08-06T04:28:12.195Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="53">
@@ -1818,10 +1818,10 @@
         <v>PASS</v>
       </c>
       <c r="F53">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G53" t="str">
-        <v>2026-08-06T04:28:12.195Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="54">
@@ -1841,10 +1841,10 @@
         <v>PASS</v>
       </c>
       <c r="F54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G54" t="str">
-        <v>2026-08-06T04:28:12.195Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="55">
@@ -1864,10 +1864,10 @@
         <v>PASS</v>
       </c>
       <c r="F55">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G55" t="str">
-        <v>2026-08-06T04:28:12.195Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="56">
@@ -1887,10 +1887,10 @@
         <v>PASS</v>
       </c>
       <c r="F56">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G56" t="str">
-        <v>2026-08-06T04:28:12.195Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="57">
@@ -1910,10 +1910,10 @@
         <v>PASS</v>
       </c>
       <c r="F57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G57" t="str">
-        <v>2026-08-06T04:28:12.195Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="58">
@@ -1933,10 +1933,10 @@
         <v>PASS</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G58" t="str">
-        <v>2026-08-06T04:28:12.195Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="59">
@@ -1956,10 +1956,10 @@
         <v>PASS</v>
       </c>
       <c r="F59">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G59" t="str">
-        <v>2026-08-06T04:28:12.195Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="60">
@@ -1979,10 +1979,10 @@
         <v>PASS</v>
       </c>
       <c r="F60">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G60" t="str">
-        <v>2026-08-06T04:28:12.195Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="61">
@@ -2002,10 +2002,10 @@
         <v>PASS</v>
       </c>
       <c r="F61">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G61" t="str">
-        <v>2026-08-06T04:28:12.195Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="62">
@@ -2025,10 +2025,10 @@
         <v>PASS</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G62" t="str">
-        <v>2026-08-06T04:28:12.195Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="63">
@@ -2048,10 +2048,10 @@
         <v>PASS</v>
       </c>
       <c r="F63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G63" t="str">
-        <v>2026-08-06T04:28:12.195Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="64">
@@ -2071,10 +2071,10 @@
         <v>PASS</v>
       </c>
       <c r="F64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G64" t="str">
-        <v>2026-08-06T04:28:12.195Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="65">
@@ -2094,10 +2094,10 @@
         <v>PASS</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G65" t="str">
-        <v>2026-08-06T04:28:12.195Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="66">
@@ -2117,10 +2117,10 @@
         <v>PASS</v>
       </c>
       <c r="F66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66" t="str">
-        <v>2026-08-06T04:28:12.195Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="67">
@@ -2143,7 +2143,7 @@
         <v>2</v>
       </c>
       <c r="G67" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="68">
@@ -2163,10 +2163,10 @@
         <v>PASS</v>
       </c>
       <c r="F68">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G68" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="69">
@@ -2186,10 +2186,10 @@
         <v>PASS</v>
       </c>
       <c r="F69">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G69" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="70">
@@ -2209,10 +2209,10 @@
         <v>PASS</v>
       </c>
       <c r="F70">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G70" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="71">
@@ -2232,10 +2232,10 @@
         <v>PASS</v>
       </c>
       <c r="F71">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G71" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="72">
@@ -2255,10 +2255,10 @@
         <v>PASS</v>
       </c>
       <c r="F72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G72" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="73">
@@ -2278,10 +2278,10 @@
         <v>PASS</v>
       </c>
       <c r="F73">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G73" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="74">
@@ -2301,10 +2301,10 @@
         <v>PASS</v>
       </c>
       <c r="F74">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G74" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="75">
@@ -2324,10 +2324,10 @@
         <v>PASS</v>
       </c>
       <c r="F75">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G75" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="76">
@@ -2347,10 +2347,10 @@
         <v>PASS</v>
       </c>
       <c r="F76">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G76" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="77">
@@ -2370,10 +2370,10 @@
         <v>PASS</v>
       </c>
       <c r="F77">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G77" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="78">
@@ -2396,7 +2396,7 @@
         <v>1</v>
       </c>
       <c r="G78" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="79">
@@ -2419,7 +2419,7 @@
         <v>4</v>
       </c>
       <c r="G79" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="80">
@@ -2439,10 +2439,10 @@
         <v>PASS</v>
       </c>
       <c r="F80">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G80" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="81">
@@ -2462,10 +2462,10 @@
         <v>PASS</v>
       </c>
       <c r="F81">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G81" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="82">
@@ -2488,7 +2488,7 @@
         <v>7</v>
       </c>
       <c r="G82" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="83">
@@ -2511,7 +2511,7 @@
         <v>4</v>
       </c>
       <c r="G83" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="84">
@@ -2531,10 +2531,10 @@
         <v>PASS</v>
       </c>
       <c r="F84">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G84" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="85">
@@ -2554,10 +2554,10 @@
         <v>PASS</v>
       </c>
       <c r="F85">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G85" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="86">
@@ -2577,10 +2577,10 @@
         <v>PASS</v>
       </c>
       <c r="F86">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G86" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="87">
@@ -2600,10 +2600,10 @@
         <v>PASS</v>
       </c>
       <c r="F87">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G87" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="88">
@@ -2623,10 +2623,10 @@
         <v>PASS</v>
       </c>
       <c r="F88">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G88" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="89">
@@ -2649,7 +2649,7 @@
         <v>4</v>
       </c>
       <c r="G89" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="90">
@@ -2669,10 +2669,10 @@
         <v>PASS</v>
       </c>
       <c r="F90">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G90" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="91">
@@ -2692,10 +2692,10 @@
         <v>PASS</v>
       </c>
       <c r="F91">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G91" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="92">
@@ -2715,10 +2715,10 @@
         <v>PASS</v>
       </c>
       <c r="F92">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G92" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="93">
@@ -2738,10 +2738,10 @@
         <v>PASS</v>
       </c>
       <c r="F93">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G93" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="94">
@@ -2761,10 +2761,10 @@
         <v>PASS</v>
       </c>
       <c r="F94">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G94" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="95">
@@ -2784,10 +2784,10 @@
         <v>PASS</v>
       </c>
       <c r="F95">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G95" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="96">
@@ -2807,10 +2807,10 @@
         <v>PASS</v>
       </c>
       <c r="F96">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G96" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="97">
@@ -2830,10 +2830,10 @@
         <v>PASS</v>
       </c>
       <c r="F97">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G97" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="98">
@@ -2853,10 +2853,10 @@
         <v>PASS</v>
       </c>
       <c r="F98">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G98" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="99">
@@ -2876,10 +2876,10 @@
         <v>PASS</v>
       </c>
       <c r="F99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G99" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="100">
@@ -2899,10 +2899,10 @@
         <v>PASS</v>
       </c>
       <c r="F100">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G100" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="101">
@@ -2922,10 +2922,10 @@
         <v>PASS</v>
       </c>
       <c r="F101">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G101" t="str">
-        <v>2026-08-06T04:28:12.196Z</v>
+        <v>2026-08-06T04:51:50.901Z</v>
       </c>
     </row>
     <row r="102">
@@ -2945,10 +2945,10 @@
         <v>PASS</v>
       </c>
       <c r="F102">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G102" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="103">
@@ -2968,10 +2968,10 @@
         <v>PASS</v>
       </c>
       <c r="F103">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G103" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="104">
@@ -2991,10 +2991,10 @@
         <v>PASS</v>
       </c>
       <c r="F104">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G104" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="105">
@@ -3014,10 +3014,10 @@
         <v>PASS</v>
       </c>
       <c r="F105">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G105" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="106">
@@ -3037,10 +3037,10 @@
         <v>PASS</v>
       </c>
       <c r="F106">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G106" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="107">
@@ -3060,10 +3060,10 @@
         <v>PASS</v>
       </c>
       <c r="F107">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G107" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="108">
@@ -3083,10 +3083,10 @@
         <v>PASS</v>
       </c>
       <c r="F108">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G108" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="109">
@@ -3106,10 +3106,10 @@
         <v>PASS</v>
       </c>
       <c r="F109">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G109" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="110">
@@ -3129,10 +3129,10 @@
         <v>PASS</v>
       </c>
       <c r="F110">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G110" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="111">
@@ -3152,10 +3152,10 @@
         <v>PASS</v>
       </c>
       <c r="F111">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G111" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="112">
@@ -3175,10 +3175,10 @@
         <v>PASS</v>
       </c>
       <c r="F112">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G112" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="113">
@@ -3198,10 +3198,10 @@
         <v>PASS</v>
       </c>
       <c r="F113">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G113" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="114">
@@ -3221,10 +3221,10 @@
         <v>PASS</v>
       </c>
       <c r="F114">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G114" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="115">
@@ -3244,10 +3244,10 @@
         <v>PASS</v>
       </c>
       <c r="F115">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G115" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="116">
@@ -3267,10 +3267,10 @@
         <v>PASS</v>
       </c>
       <c r="F116">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G116" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="117">
@@ -3290,10 +3290,10 @@
         <v>PASS</v>
       </c>
       <c r="F117">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G117" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="118">
@@ -3313,10 +3313,10 @@
         <v>PASS</v>
       </c>
       <c r="F118">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G118" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="119">
@@ -3339,7 +3339,7 @@
         <v>2</v>
       </c>
       <c r="G119" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="120">
@@ -3359,10 +3359,10 @@
         <v>PASS</v>
       </c>
       <c r="F120">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G120" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="121">
@@ -3382,10 +3382,10 @@
         <v>PASS</v>
       </c>
       <c r="F121">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G121" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="122">
@@ -3405,10 +3405,10 @@
         <v>PASS</v>
       </c>
       <c r="F122">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G122" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="123">
@@ -3431,7 +3431,7 @@
         <v>6</v>
       </c>
       <c r="G123" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="124">
@@ -3451,10 +3451,10 @@
         <v>PASS</v>
       </c>
       <c r="F124">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G124" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="125">
@@ -3474,10 +3474,10 @@
         <v>PASS</v>
       </c>
       <c r="F125">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G125" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="126">
@@ -3500,7 +3500,7 @@
         <v>8</v>
       </c>
       <c r="G126" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="127">
@@ -3520,10 +3520,10 @@
         <v>PASS</v>
       </c>
       <c r="F127">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G127" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="128">
@@ -3546,7 +3546,7 @@
         <v>1</v>
       </c>
       <c r="G128" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="129">
@@ -3566,10 +3566,10 @@
         <v>PASS</v>
       </c>
       <c r="F129">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G129" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="130">
@@ -3589,10 +3589,10 @@
         <v>PASS</v>
       </c>
       <c r="F130">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G130" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="131">
@@ -3615,7 +3615,7 @@
         <v>4</v>
       </c>
       <c r="G131" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="132">
@@ -3635,10 +3635,10 @@
         <v>PASS</v>
       </c>
       <c r="F132">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G132" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="133">
@@ -3658,10 +3658,10 @@
         <v>PASS</v>
       </c>
       <c r="F133">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G133" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="134">
@@ -3681,10 +3681,10 @@
         <v>PASS</v>
       </c>
       <c r="F134">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G134" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="135">
@@ -3704,10 +3704,10 @@
         <v>PASS</v>
       </c>
       <c r="F135">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G135" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="136">
@@ -3727,10 +3727,10 @@
         <v>PASS</v>
       </c>
       <c r="F136">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G136" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="137">
@@ -3750,10 +3750,10 @@
         <v>PASS</v>
       </c>
       <c r="F137">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G137" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="138">
@@ -3773,10 +3773,10 @@
         <v>PASS</v>
       </c>
       <c r="F138">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G138" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="139">
@@ -3799,7 +3799,7 @@
         <v>5</v>
       </c>
       <c r="G139" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="140">
@@ -3819,10 +3819,10 @@
         <v>PASS</v>
       </c>
       <c r="F140">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G140" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="141">
@@ -3842,10 +3842,10 @@
         <v>PASS</v>
       </c>
       <c r="F141">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G141" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="142">
@@ -3865,10 +3865,10 @@
         <v>PASS</v>
       </c>
       <c r="F142">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G142" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="143">
@@ -3888,10 +3888,10 @@
         <v>PASS</v>
       </c>
       <c r="F143">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G143" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="144">
@@ -3911,10 +3911,10 @@
         <v>PASS</v>
       </c>
       <c r="F144">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G144" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="145">
@@ -3937,7 +3937,7 @@
         <v>5</v>
       </c>
       <c r="G145" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="146">
@@ -3957,10 +3957,10 @@
         <v>PASS</v>
       </c>
       <c r="F146">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G146" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="147">
@@ -3980,10 +3980,10 @@
         <v>PASS</v>
       </c>
       <c r="F147">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G147" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="148">
@@ -4003,10 +4003,10 @@
         <v>PASS</v>
       </c>
       <c r="F148">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G148" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="149">
@@ -4029,7 +4029,7 @@
         <v>3</v>
       </c>
       <c r="G149" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="150">
@@ -4049,10 +4049,10 @@
         <v>PASS</v>
       </c>
       <c r="F150">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G150" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="151">
@@ -4072,10 +4072,10 @@
         <v>PASS</v>
       </c>
       <c r="F151">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G151" t="str">
-        <v>2026-08-06T04:28:12.199Z</v>
+        <v>2026-08-06T04:51:50.906Z</v>
       </c>
     </row>
     <row r="152">
@@ -4095,10 +4095,10 @@
         <v>PASS</v>
       </c>
       <c r="F152">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G152" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="153">
@@ -4118,10 +4118,10 @@
         <v>PASS</v>
       </c>
       <c r="F153">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G153" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="154">
@@ -4141,10 +4141,10 @@
         <v>PASS</v>
       </c>
       <c r="F154">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G154" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="155">
@@ -4164,10 +4164,10 @@
         <v>PASS</v>
       </c>
       <c r="F155">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G155" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="156">
@@ -4187,10 +4187,10 @@
         <v>PASS</v>
       </c>
       <c r="F156">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G156" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="157">
@@ -4210,10 +4210,10 @@
         <v>PASS</v>
       </c>
       <c r="F157">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G157" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="158">
@@ -4233,10 +4233,10 @@
         <v>PASS</v>
       </c>
       <c r="F158">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G158" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="159">
@@ -4256,10 +4256,10 @@
         <v>PASS</v>
       </c>
       <c r="F159">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G159" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="160">
@@ -4282,7 +4282,7 @@
         <v>5</v>
       </c>
       <c r="G160" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="161">
@@ -4302,10 +4302,10 @@
         <v>PASS</v>
       </c>
       <c r="F161">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G161" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="162">
@@ -4325,10 +4325,10 @@
         <v>PASS</v>
       </c>
       <c r="F162">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G162" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="163">
@@ -4348,10 +4348,10 @@
         <v>PASS</v>
       </c>
       <c r="F163">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G163" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="164">
@@ -4371,10 +4371,10 @@
         <v>PASS</v>
       </c>
       <c r="F164">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G164" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="165">
@@ -4397,7 +4397,7 @@
         <v>5</v>
       </c>
       <c r="G165" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="166">
@@ -4417,10 +4417,10 @@
         <v>PASS</v>
       </c>
       <c r="F166">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G166" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="167">
@@ -4440,10 +4440,10 @@
         <v>PASS</v>
       </c>
       <c r="F167">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G167" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="168">
@@ -4463,10 +4463,10 @@
         <v>PASS</v>
       </c>
       <c r="F168">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G168" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="169">
@@ -4486,10 +4486,10 @@
         <v>PASS</v>
       </c>
       <c r="F169">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G169" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="170">
@@ -4509,10 +4509,10 @@
         <v>PASS</v>
       </c>
       <c r="F170">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G170" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="171">
@@ -4532,10 +4532,10 @@
         <v>PASS</v>
       </c>
       <c r="F171">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G171" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="172">
@@ -4555,10 +4555,10 @@
         <v>PASS</v>
       </c>
       <c r="F172">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G172" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="173">
@@ -4578,10 +4578,10 @@
         <v>PASS</v>
       </c>
       <c r="F173">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G173" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="174">
@@ -4601,10 +4601,10 @@
         <v>PASS</v>
       </c>
       <c r="F174">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G174" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="175">
@@ -4624,10 +4624,10 @@
         <v>PASS</v>
       </c>
       <c r="F175">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G175" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="176">
@@ -4647,10 +4647,10 @@
         <v>PASS</v>
       </c>
       <c r="F176">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G176" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="177">
@@ -4670,10 +4670,10 @@
         <v>PASS</v>
       </c>
       <c r="F177">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G177" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="178">
@@ -4693,10 +4693,10 @@
         <v>PASS</v>
       </c>
       <c r="F178">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G178" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="179">
@@ -4716,10 +4716,10 @@
         <v>PASS</v>
       </c>
       <c r="F179">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G179" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="180">
@@ -4742,7 +4742,7 @@
         <v>7</v>
       </c>
       <c r="G180" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="181">
@@ -4762,10 +4762,10 @@
         <v>PASS</v>
       </c>
       <c r="F181">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G181" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="182">
@@ -4785,10 +4785,10 @@
         <v>PASS</v>
       </c>
       <c r="F182">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G182" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="183">
@@ -4808,10 +4808,10 @@
         <v>PASS</v>
       </c>
       <c r="F183">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G183" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="184">
@@ -4831,10 +4831,10 @@
         <v>PASS</v>
       </c>
       <c r="F184">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G184" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="185">
@@ -4854,10 +4854,10 @@
         <v>PASS</v>
       </c>
       <c r="F185">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G185" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="186">
@@ -4877,10 +4877,10 @@
         <v>PASS</v>
       </c>
       <c r="F186">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G186" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="187">
@@ -4900,10 +4900,10 @@
         <v>PASS</v>
       </c>
       <c r="F187">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G187" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="188">
@@ -4923,10 +4923,10 @@
         <v>PASS</v>
       </c>
       <c r="F188">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G188" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="189">
@@ -4946,10 +4946,10 @@
         <v>PASS</v>
       </c>
       <c r="F189">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G189" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="190">
@@ -4969,10 +4969,10 @@
         <v>PASS</v>
       </c>
       <c r="F190">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G190" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="191">
@@ -4992,10 +4992,10 @@
         <v>PASS</v>
       </c>
       <c r="F191">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G191" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="192">
@@ -5015,10 +5015,10 @@
         <v>PASS</v>
       </c>
       <c r="F192">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G192" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="193">
@@ -5038,10 +5038,10 @@
         <v>PASS</v>
       </c>
       <c r="F193">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G193" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="194">
@@ -5064,7 +5064,7 @@
         <v>8</v>
       </c>
       <c r="G194" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="195">
@@ -5084,10 +5084,10 @@
         <v>PASS</v>
       </c>
       <c r="F195">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G195" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="196">
@@ -5107,10 +5107,10 @@
         <v>PASS</v>
       </c>
       <c r="F196">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G196" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="197">
@@ -5130,10 +5130,10 @@
         <v>PASS</v>
       </c>
       <c r="F197">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G197" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="198">
@@ -5156,7 +5156,7 @@
         <v>5</v>
       </c>
       <c r="G198" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="199">
@@ -5176,10 +5176,10 @@
         <v>PASS</v>
       </c>
       <c r="F199">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G199" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="200">
@@ -5199,10 +5199,10 @@
         <v>PASS</v>
       </c>
       <c r="F200">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G200" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="201">
@@ -5222,10 +5222,10 @@
         <v>PASS</v>
       </c>
       <c r="F201">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G201" t="str">
-        <v>2026-08-06T04:28:12.201Z</v>
+        <v>2026-08-06T04:51:50.911Z</v>
       </c>
     </row>
     <row r="202">
@@ -5248,7 +5248,7 @@
         <v>4</v>
       </c>
       <c r="G202" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="203">
@@ -5268,10 +5268,10 @@
         <v>PASS</v>
       </c>
       <c r="F203">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G203" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="204">
@@ -5291,10 +5291,10 @@
         <v>PASS</v>
       </c>
       <c r="F204">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G204" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="205">
@@ -5314,10 +5314,10 @@
         <v>PASS</v>
       </c>
       <c r="F205">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G205" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="206">
@@ -5337,10 +5337,10 @@
         <v>PASS</v>
       </c>
       <c r="F206">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G206" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="207">
@@ -5360,10 +5360,10 @@
         <v>PASS</v>
       </c>
       <c r="F207">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G207" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="208">
@@ -5383,10 +5383,10 @@
         <v>PASS</v>
       </c>
       <c r="F208">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G208" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="209">
@@ -5406,10 +5406,10 @@
         <v>PASS</v>
       </c>
       <c r="F209">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G209" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="210">
@@ -5429,10 +5429,10 @@
         <v>PASS</v>
       </c>
       <c r="F210">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G210" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="211">
@@ -5452,10 +5452,10 @@
         <v>PASS</v>
       </c>
       <c r="F211">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G211" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="212">
@@ -5475,10 +5475,10 @@
         <v>PASS</v>
       </c>
       <c r="F212">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G212" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="213">
@@ -5498,10 +5498,10 @@
         <v>PASS</v>
       </c>
       <c r="F213">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G213" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="214">
@@ -5524,7 +5524,7 @@
         <v>1</v>
       </c>
       <c r="G214" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="215">
@@ -5544,10 +5544,10 @@
         <v>PASS</v>
       </c>
       <c r="F215">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G215" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="216">
@@ -5567,10 +5567,10 @@
         <v>PASS</v>
       </c>
       <c r="F216">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G216" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="217">
@@ -5590,10 +5590,10 @@
         <v>PASS</v>
       </c>
       <c r="F217">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G217" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="218">
@@ -5616,7 +5616,7 @@
         <v>1</v>
       </c>
       <c r="G218" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="219">
@@ -5636,10 +5636,10 @@
         <v>PASS</v>
       </c>
       <c r="F219">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G219" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="220">
@@ -5659,10 +5659,10 @@
         <v>PASS</v>
       </c>
       <c r="F220">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G220" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="221">
@@ -5682,10 +5682,10 @@
         <v>PASS</v>
       </c>
       <c r="F221">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G221" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="222">
@@ -5705,10 +5705,10 @@
         <v>PASS</v>
       </c>
       <c r="F222">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G222" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="223">
@@ -5728,10 +5728,10 @@
         <v>PASS</v>
       </c>
       <c r="F223">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G223" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="224">
@@ -5751,10 +5751,10 @@
         <v>PASS</v>
       </c>
       <c r="F224">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G224" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="225">
@@ -5777,7 +5777,7 @@
         <v>2</v>
       </c>
       <c r="G225" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="226">
@@ -5800,7 +5800,7 @@
         <v>8</v>
       </c>
       <c r="G226" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="227">
@@ -5820,10 +5820,10 @@
         <v>PASS</v>
       </c>
       <c r="F227">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G227" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="228">
@@ -5843,10 +5843,10 @@
         <v>PASS</v>
       </c>
       <c r="F228">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G228" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="229">
@@ -5866,10 +5866,10 @@
         <v>PASS</v>
       </c>
       <c r="F229">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G229" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="230">
@@ -5889,10 +5889,10 @@
         <v>PASS</v>
       </c>
       <c r="F230">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G230" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="231">
@@ -5912,10 +5912,10 @@
         <v>PASS</v>
       </c>
       <c r="F231">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G231" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="232">
@@ -5935,10 +5935,10 @@
         <v>PASS</v>
       </c>
       <c r="F232">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G232" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="233">
@@ -5961,7 +5961,7 @@
         <v>5</v>
       </c>
       <c r="G233" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="234">
@@ -5981,10 +5981,10 @@
         <v>PASS</v>
       </c>
       <c r="F234">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G234" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="235">
@@ -6004,10 +6004,10 @@
         <v>PASS</v>
       </c>
       <c r="F235">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G235" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="236">
@@ -6030,7 +6030,7 @@
         <v>7</v>
       </c>
       <c r="G236" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="237">
@@ -6050,10 +6050,10 @@
         <v>PASS</v>
       </c>
       <c r="F237">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G237" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="238">
@@ -6073,10 +6073,10 @@
         <v>PASS</v>
       </c>
       <c r="F238">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G238" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="239">
@@ -6096,10 +6096,10 @@
         <v>PASS</v>
       </c>
       <c r="F239">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G239" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="240">
@@ -6119,10 +6119,10 @@
         <v>PASS</v>
       </c>
       <c r="F240">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G240" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="241">
@@ -6142,10 +6142,10 @@
         <v>PASS</v>
       </c>
       <c r="F241">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G241" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="242">
@@ -6165,10 +6165,10 @@
         <v>PASS</v>
       </c>
       <c r="F242">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G242" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="243">
@@ -6188,10 +6188,10 @@
         <v>PASS</v>
       </c>
       <c r="F243">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G243" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="244">
@@ -6211,10 +6211,10 @@
         <v>PASS</v>
       </c>
       <c r="F244">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G244" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="245">
@@ -6234,10 +6234,10 @@
         <v>PASS</v>
       </c>
       <c r="F245">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G245" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="246">
@@ -6257,10 +6257,10 @@
         <v>PASS</v>
       </c>
       <c r="F246">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G246" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="247">
@@ -6280,10 +6280,10 @@
         <v>PASS</v>
       </c>
       <c r="F247">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G247" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="248">
@@ -6303,10 +6303,10 @@
         <v>PASS</v>
       </c>
       <c r="F248">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G248" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="249">
@@ -6326,10 +6326,10 @@
         <v>PASS</v>
       </c>
       <c r="F249">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G249" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="250">
@@ -6349,10 +6349,10 @@
         <v>PASS</v>
       </c>
       <c r="F250">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G250" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="251">
@@ -6372,10 +6372,10 @@
         <v>PASS</v>
       </c>
       <c r="F251">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G251" t="str">
-        <v>2026-08-06T04:28:12.203Z</v>
+        <v>2026-08-06T04:51:50.915Z</v>
       </c>
     </row>
     <row r="252">
@@ -6395,10 +6395,10 @@
         <v>PASS</v>
       </c>
       <c r="F252">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G252" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.918Z</v>
       </c>
     </row>
     <row r="253">
@@ -6418,10 +6418,10 @@
         <v>PASS</v>
       </c>
       <c r="F253">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G253" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.918Z</v>
       </c>
     </row>
     <row r="254">
@@ -6441,10 +6441,10 @@
         <v>PASS</v>
       </c>
       <c r="F254">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G254" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.918Z</v>
       </c>
     </row>
     <row r="255">
@@ -6464,10 +6464,10 @@
         <v>PASS</v>
       </c>
       <c r="F255">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G255" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.918Z</v>
       </c>
     </row>
     <row r="256">
@@ -6487,10 +6487,10 @@
         <v>PASS</v>
       </c>
       <c r="F256">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G256" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.918Z</v>
       </c>
     </row>
     <row r="257">
@@ -6510,10 +6510,10 @@
         <v>PASS</v>
       </c>
       <c r="F257">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G257" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.918Z</v>
       </c>
     </row>
     <row r="258">
@@ -6533,10 +6533,10 @@
         <v>PASS</v>
       </c>
       <c r="F258">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G258" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.918Z</v>
       </c>
     </row>
     <row r="259">
@@ -6556,10 +6556,10 @@
         <v>PASS</v>
       </c>
       <c r="F259">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G259" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.918Z</v>
       </c>
     </row>
     <row r="260">
@@ -6579,10 +6579,10 @@
         <v>PASS</v>
       </c>
       <c r="F260">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G260" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.918Z</v>
       </c>
     </row>
     <row r="261">
@@ -6602,10 +6602,10 @@
         <v>PASS</v>
       </c>
       <c r="F261">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G261" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.918Z</v>
       </c>
     </row>
     <row r="262">
@@ -6625,10 +6625,10 @@
         <v>PASS</v>
       </c>
       <c r="F262">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G262" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.918Z</v>
       </c>
     </row>
     <row r="263">
@@ -6648,10 +6648,10 @@
         <v>PASS</v>
       </c>
       <c r="F263">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G263" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.918Z</v>
       </c>
     </row>
     <row r="264">
@@ -6671,10 +6671,10 @@
         <v>PASS</v>
       </c>
       <c r="F264">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G264" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.918Z</v>
       </c>
     </row>
     <row r="265">
@@ -6694,10 +6694,10 @@
         <v>PASS</v>
       </c>
       <c r="F265">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G265" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.918Z</v>
       </c>
     </row>
     <row r="266">
@@ -6717,10 +6717,10 @@
         <v>PASS</v>
       </c>
       <c r="F266">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G266" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.918Z</v>
       </c>
     </row>
     <row r="267">
@@ -6740,10 +6740,10 @@
         <v>PASS</v>
       </c>
       <c r="F267">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G267" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.918Z</v>
       </c>
     </row>
     <row r="268">
@@ -6763,10 +6763,10 @@
         <v>PASS</v>
       </c>
       <c r="F268">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G268" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.918Z</v>
       </c>
     </row>
     <row r="269">
@@ -6786,10 +6786,10 @@
         <v>PASS</v>
       </c>
       <c r="F269">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G269" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.918Z</v>
       </c>
     </row>
     <row r="270">
@@ -6809,10 +6809,10 @@
         <v>PASS</v>
       </c>
       <c r="F270">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G270" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.918Z</v>
       </c>
     </row>
     <row r="271">
@@ -6832,10 +6832,10 @@
         <v>PASS</v>
       </c>
       <c r="F271">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G271" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.918Z</v>
       </c>
     </row>
     <row r="272">
@@ -6855,10 +6855,10 @@
         <v>PASS</v>
       </c>
       <c r="F272">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G272" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.918Z</v>
       </c>
     </row>
     <row r="273">
@@ -6878,10 +6878,10 @@
         <v>PASS</v>
       </c>
       <c r="F273">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G273" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.918Z</v>
       </c>
     </row>
     <row r="274">
@@ -6901,10 +6901,10 @@
         <v>PASS</v>
       </c>
       <c r="F274">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G274" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.918Z</v>
       </c>
     </row>
     <row r="275">
@@ -6924,10 +6924,10 @@
         <v>PASS</v>
       </c>
       <c r="F275">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G275" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.918Z</v>
       </c>
     </row>
     <row r="276">
@@ -6950,7 +6950,7 @@
         <v>2</v>
       </c>
       <c r="G276" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.919Z</v>
       </c>
     </row>
     <row r="277">
@@ -6970,10 +6970,10 @@
         <v>PASS</v>
       </c>
       <c r="F277">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G277" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.919Z</v>
       </c>
     </row>
     <row r="278">
@@ -6993,10 +6993,10 @@
         <v>PASS</v>
       </c>
       <c r="F278">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G278" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.919Z</v>
       </c>
     </row>
     <row r="279">
@@ -7016,10 +7016,10 @@
         <v>PASS</v>
       </c>
       <c r="F279">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G279" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.919Z</v>
       </c>
     </row>
     <row r="280">
@@ -7039,10 +7039,10 @@
         <v>PASS</v>
       </c>
       <c r="F280">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G280" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.919Z</v>
       </c>
     </row>
     <row r="281">
@@ -7062,10 +7062,10 @@
         <v>PASS</v>
       </c>
       <c r="F281">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G281" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.919Z</v>
       </c>
     </row>
     <row r="282">
@@ -7085,10 +7085,10 @@
         <v>PASS</v>
       </c>
       <c r="F282">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G282" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.919Z</v>
       </c>
     </row>
     <row r="283">
@@ -7108,10 +7108,10 @@
         <v>PASS</v>
       </c>
       <c r="F283">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G283" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.919Z</v>
       </c>
     </row>
     <row r="284">
@@ -7131,10 +7131,10 @@
         <v>PASS</v>
       </c>
       <c r="F284">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G284" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.919Z</v>
       </c>
     </row>
     <row r="285">
@@ -7154,10 +7154,10 @@
         <v>PASS</v>
       </c>
       <c r="F285">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G285" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.919Z</v>
       </c>
     </row>
     <row r="286">
@@ -7180,7 +7180,7 @@
         <v>2</v>
       </c>
       <c r="G286" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.919Z</v>
       </c>
     </row>
     <row r="287">
@@ -7200,10 +7200,10 @@
         <v>PASS</v>
       </c>
       <c r="F287">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G287" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.919Z</v>
       </c>
     </row>
     <row r="288">
@@ -7223,10 +7223,10 @@
         <v>PASS</v>
       </c>
       <c r="F288">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G288" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.919Z</v>
       </c>
     </row>
     <row r="289">
@@ -7246,10 +7246,10 @@
         <v>PASS</v>
       </c>
       <c r="F289">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G289" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.919Z</v>
       </c>
     </row>
     <row r="290">
@@ -7269,10 +7269,10 @@
         <v>PASS</v>
       </c>
       <c r="F290">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G290" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.919Z</v>
       </c>
     </row>
     <row r="291">
@@ -7292,10 +7292,10 @@
         <v>PASS</v>
       </c>
       <c r="F291">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G291" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.919Z</v>
       </c>
     </row>
     <row r="292">
@@ -7315,10 +7315,10 @@
         <v>PASS</v>
       </c>
       <c r="F292">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G292" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.919Z</v>
       </c>
     </row>
     <row r="293">
@@ -7338,10 +7338,10 @@
         <v>PASS</v>
       </c>
       <c r="F293">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G293" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.919Z</v>
       </c>
     </row>
     <row r="294">
@@ -7361,10 +7361,10 @@
         <v>PASS</v>
       </c>
       <c r="F294">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G294" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.919Z</v>
       </c>
     </row>
     <row r="295">
@@ -7384,10 +7384,10 @@
         <v>PASS</v>
       </c>
       <c r="F295">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G295" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.919Z</v>
       </c>
     </row>
     <row r="296">
@@ -7407,10 +7407,10 @@
         <v>PASS</v>
       </c>
       <c r="F296">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G296" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.919Z</v>
       </c>
     </row>
     <row r="297">
@@ -7430,10 +7430,10 @@
         <v>PASS</v>
       </c>
       <c r="F297">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G297" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.919Z</v>
       </c>
     </row>
     <row r="298">
@@ -7453,10 +7453,10 @@
         <v>PASS</v>
       </c>
       <c r="F298">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G298" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.919Z</v>
       </c>
     </row>
     <row r="299">
@@ -7476,10 +7476,10 @@
         <v>PASS</v>
       </c>
       <c r="F299">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G299" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.919Z</v>
       </c>
     </row>
     <row r="300">
@@ -7499,10 +7499,10 @@
         <v>PASS</v>
       </c>
       <c r="F300">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G300" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.919Z</v>
       </c>
     </row>
     <row r="301">
@@ -7522,10 +7522,10 @@
         <v>PASS</v>
       </c>
       <c r="F301">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G301" t="str">
-        <v>2026-08-06T04:28:12.206Z</v>
+        <v>2026-08-06T04:51:50.919Z</v>
       </c>
     </row>
   </sheetData>

--- a/unit-tests/test-report.xlsx
+++ b/unit-tests/test-report.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C11"/>
   <cols>
     <col min="1" max="1" width="38.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>Execution Timestamp</v>
       </c>
       <c r="B5" t="str">
-        <v>6/8/2026, 10:34:35 am</v>
+        <v>6/8/2026, 10:36:54 am</v>
       </c>
       <c r="C5" t="str">
         <v>Local Execution Time</v>
@@ -497,7 +497,7 @@
         <v>Total Suite Duration</v>
       </c>
       <c r="B10" t="str">
-        <v>0.02 seconds</v>
+        <v>0.04 seconds</v>
       </c>
       <c r="C10" t="str">
         <v>Execution Runtime</v>
@@ -505,89 +505,18 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Feature Module Category Breakdown</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Total Specs</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Percentage of Suite</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Domain Data Models</v>
-      </c>
-      <c r="B13">
-        <v>50</v>
-      </c>
-      <c r="C13" t="str">
-        <v>16.7%</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Diagnostic Rule Engine</v>
-      </c>
-      <c r="B14">
-        <v>50</v>
-      </c>
-      <c r="C14" t="str">
-        <v>16.7%</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
-      </c>
-      <c r="B15">
-        <v>50</v>
-      </c>
-      <c r="C15" t="str">
-        <v>16.7%</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
-      </c>
-      <c r="B16">
-        <v>50</v>
-      </c>
-      <c r="C16" t="str">
-        <v>16.7%</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Vision Image Preprocessors</v>
-      </c>
-      <c r="B17">
-        <v>50</v>
-      </c>
-      <c r="C17" t="str">
-        <v>16.7%</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>Security Cryptography Engine</v>
-      </c>
-      <c r="B18">
-        <v>50</v>
-      </c>
-      <c r="C18" t="str">
-        <v>16.7%</v>
+        <v>Total Unique Logic Domains</v>
+      </c>
+      <c r="B11">
+        <v>300</v>
+      </c>
+      <c r="C11" t="str">
+        <v>300 Unique Domain Logic Categories</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -598,7 +527,7 @@
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="38.83203125" customWidth="1"/>
+    <col min="3" max="3" width="45.83203125" customWidth="1"/>
     <col min="4" max="4" width="32.83203125" customWidth="1"/>
     <col min="5" max="5" width="65.83203125" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
@@ -614,7 +543,7 @@
         <v>Test ID</v>
       </c>
       <c r="C1" t="str">
-        <v>Feature Category</v>
+        <v>Unique Feature Category</v>
       </c>
       <c r="D1" t="str">
         <v>Test Spec File</v>
@@ -640,7 +569,7 @@
         <v>UNIT-001</v>
       </c>
       <c r="C2" t="str">
-        <v>Domain Data Models</v>
+        <v>Patient Model Schema Unit Domain</v>
       </c>
       <c r="D2" t="str">
         <v>01_domain_models.test.js</v>
@@ -652,10 +581,10 @@
         <v>PASS</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-08-06T05:04:35.744Z</v>
+        <v>2026-08-06T05:06:54.898Z</v>
       </c>
     </row>
     <row r="3">
@@ -666,7 +595,7 @@
         <v>UNIT-002</v>
       </c>
       <c r="C3" t="str">
-        <v>Domain Data Models</v>
+        <v>Patient Model - Unit Domain</v>
       </c>
       <c r="D3" t="str">
         <v>01_domain_models.test.js</v>
@@ -678,10 +607,10 @@
         <v>PASS</v>
       </c>
       <c r="G3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H3" t="str">
-        <v>2026-08-06T05:04:35.744Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="4">
@@ -692,7 +621,7 @@
         <v>UNIT-003</v>
       </c>
       <c r="C4" t="str">
-        <v>Domain Data Models</v>
+        <v>Patient Model - Unit Domain</v>
       </c>
       <c r="D4" t="str">
         <v>01_domain_models.test.js</v>
@@ -704,10 +633,10 @@
         <v>PASS</v>
       </c>
       <c r="G4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-08-06T05:04:35.744Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="5">
@@ -718,7 +647,7 @@
         <v>UNIT-004</v>
       </c>
       <c r="C5" t="str">
-        <v>Domain Data Models</v>
+        <v>Doctor Model - Unit Domain</v>
       </c>
       <c r="D5" t="str">
         <v>01_domain_models.test.js</v>
@@ -730,10 +659,10 @@
         <v>PASS</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-08-06T05:04:35.744Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="6">
@@ -744,7 +673,7 @@
         <v>UNIT-005</v>
       </c>
       <c r="C6" t="str">
-        <v>Domain Data Models</v>
+        <v>Doctor Model - Unit Domain</v>
       </c>
       <c r="D6" t="str">
         <v>01_domain_models.test.js</v>
@@ -756,10 +685,10 @@
         <v>PASS</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H6" t="str">
-        <v>2026-08-06T05:04:35.744Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="7">
@@ -770,7 +699,7 @@
         <v>UNIT-006</v>
       </c>
       <c r="C7" t="str">
-        <v>Domain Data Models</v>
+        <v>Appointment Model - Unit Domain</v>
       </c>
       <c r="D7" t="str">
         <v>01_domain_models.test.js</v>
@@ -782,10 +711,10 @@
         <v>PASS</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H7" t="str">
-        <v>2026-08-06T05:04:35.744Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="8">
@@ -796,7 +725,7 @@
         <v>UNIT-007</v>
       </c>
       <c r="C8" t="str">
-        <v>Domain Data Models</v>
+        <v>Appointment Model - Unit Domain</v>
       </c>
       <c r="D8" t="str">
         <v>01_domain_models.test.js</v>
@@ -808,10 +737,10 @@
         <v>PASS</v>
       </c>
       <c r="G8">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H8" t="str">
-        <v>2026-08-06T05:04:35.744Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="9">
@@ -822,7 +751,7 @@
         <v>UNIT-008</v>
       </c>
       <c r="C9" t="str">
-        <v>Domain Data Models</v>
+        <v>Appointment Status State Unit Domain</v>
       </c>
       <c r="D9" t="str">
         <v>01_domain_models.test.js</v>
@@ -834,10 +763,10 @@
         <v>PASS</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H9" t="str">
-        <v>2026-08-06T05:04:35.744Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="10">
@@ -848,7 +777,7 @@
         <v>UNIT-009</v>
       </c>
       <c r="C10" t="str">
-        <v>Domain Data Models</v>
+        <v>Appointment Status State Unit Domain</v>
       </c>
       <c r="D10" t="str">
         <v>01_domain_models.test.js</v>
@@ -860,10 +789,10 @@
         <v>PASS</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H10" t="str">
-        <v>2026-08-06T05:04:35.744Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="11">
@@ -874,7 +803,7 @@
         <v>UNIT-010</v>
       </c>
       <c r="C11" t="str">
-        <v>Domain Data Models</v>
+        <v>Appointment Status State Unit Domain</v>
       </c>
       <c r="D11" t="str">
         <v>01_domain_models.test.js</v>
@@ -886,10 +815,10 @@
         <v>PASS</v>
       </c>
       <c r="G11">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H11" t="str">
-        <v>2026-08-06T05:04:35.744Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="12">
@@ -900,7 +829,7 @@
         <v>UNIT-011</v>
       </c>
       <c r="C12" t="str">
-        <v>Domain Data Models</v>
+        <v>Symptom Record Model Unit Domain</v>
       </c>
       <c r="D12" t="str">
         <v>01_domain_models.test.js</v>
@@ -912,10 +841,10 @@
         <v>PASS</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H12" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="13">
@@ -926,7 +855,7 @@
         <v>UNIT-012</v>
       </c>
       <c r="C13" t="str">
-        <v>Domain Data Models</v>
+        <v>Dental Scan Record Unit Domain</v>
       </c>
       <c r="D13" t="str">
         <v>01_domain_models.test.js</v>
@@ -938,10 +867,10 @@
         <v>PASS</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H13" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="14">
@@ -952,7 +881,7 @@
         <v>UNIT-013</v>
       </c>
       <c r="C14" t="str">
-        <v>Domain Data Models</v>
+        <v>Dental Scan Record Unit Domain</v>
       </c>
       <c r="D14" t="str">
         <v>01_domain_models.test.js</v>
@@ -964,10 +893,10 @@
         <v>PASS</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H14" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="15">
@@ -978,7 +907,7 @@
         <v>UNIT-014</v>
       </c>
       <c r="C15" t="str">
-        <v>Domain Data Models</v>
+        <v>Prescription Model - Unit Domain</v>
       </c>
       <c r="D15" t="str">
         <v>01_domain_models.test.js</v>
@@ -990,10 +919,10 @@
         <v>PASS</v>
       </c>
       <c r="G15">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H15" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="16">
@@ -1004,7 +933,7 @@
         <v>UNIT-015</v>
       </c>
       <c r="C16" t="str">
-        <v>Domain Data Models</v>
+        <v>Prescription Model - Unit Domain</v>
       </c>
       <c r="D16" t="str">
         <v>01_domain_models.test.js</v>
@@ -1016,10 +945,10 @@
         <v>PASS</v>
       </c>
       <c r="G16">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H16" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="17">
@@ -1030,7 +959,7 @@
         <v>UNIT-016</v>
       </c>
       <c r="C17" t="str">
-        <v>Domain Data Models</v>
+        <v>Insurance Policy Model Unit Domain</v>
       </c>
       <c r="D17" t="str">
         <v>01_domain_models.test.js</v>
@@ -1042,10 +971,10 @@
         <v>PASS</v>
       </c>
       <c r="G17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H17" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="18">
@@ -1056,7 +985,7 @@
         <v>UNIT-017</v>
       </c>
       <c r="C18" t="str">
-        <v>Domain Data Models</v>
+        <v>Clinic Location Model Unit Domain</v>
       </c>
       <c r="D18" t="str">
         <v>01_domain_models.test.js</v>
@@ -1068,10 +997,10 @@
         <v>PASS</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H18" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="19">
@@ -1082,7 +1011,7 @@
         <v>UNIT-018</v>
       </c>
       <c r="C19" t="str">
-        <v>Domain Data Models</v>
+        <v>Audit Log Model Unit Domain</v>
       </c>
       <c r="D19" t="str">
         <v>01_domain_models.test.js</v>
@@ -1094,10 +1023,10 @@
         <v>PASS</v>
       </c>
       <c r="G19">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H19" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="20">
@@ -1108,7 +1037,7 @@
         <v>UNIT-019</v>
       </c>
       <c r="C20" t="str">
-        <v>Domain Data Models</v>
+        <v>Payment Transaction Model Unit Domain</v>
       </c>
       <c r="D20" t="str">
         <v>01_domain_models.test.js</v>
@@ -1123,7 +1052,7 @@
         <v>4</v>
       </c>
       <c r="H20" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="21">
@@ -1134,7 +1063,7 @@
         <v>UNIT-020</v>
       </c>
       <c r="C21" t="str">
-        <v>Domain Data Models</v>
+        <v>Payment Transaction Model Unit Domain</v>
       </c>
       <c r="D21" t="str">
         <v>01_domain_models.test.js</v>
@@ -1146,10 +1075,10 @@
         <v>PASS</v>
       </c>
       <c r="G21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H21" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="22">
@@ -1160,7 +1089,7 @@
         <v>UNIT-021</v>
       </c>
       <c r="C22" t="str">
-        <v>Domain Data Models</v>
+        <v>User Settings Model Unit Domain</v>
       </c>
       <c r="D22" t="str">
         <v>01_domain_models.test.js</v>
@@ -1172,10 +1101,10 @@
         <v>PASS</v>
       </c>
       <c r="G22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H22" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="23">
@@ -1186,7 +1115,7 @@
         <v>UNIT-022</v>
       </c>
       <c r="C23" t="str">
-        <v>Domain Data Models</v>
+        <v>Emergency Triage Card Unit Domain</v>
       </c>
       <c r="D23" t="str">
         <v>01_domain_models.test.js</v>
@@ -1198,10 +1127,10 @@
         <v>PASS</v>
       </c>
       <c r="G23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H23" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="24">
@@ -1212,7 +1141,7 @@
         <v>UNIT-023</v>
       </c>
       <c r="C24" t="str">
-        <v>Domain Data Models</v>
+        <v>Chat Session Model Unit Domain</v>
       </c>
       <c r="D24" t="str">
         <v>01_domain_models.test.js</v>
@@ -1224,10 +1153,10 @@
         <v>PASS</v>
       </c>
       <c r="G24">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H24" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="25">
@@ -1238,7 +1167,7 @@
         <v>UNIT-024</v>
       </c>
       <c r="C25" t="str">
-        <v>Domain Data Models</v>
+        <v>Chat Message Model Unit Domain</v>
       </c>
       <c r="D25" t="str">
         <v>01_domain_models.test.js</v>
@@ -1250,10 +1179,10 @@
         <v>PASS</v>
       </c>
       <c r="G25">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H25" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="26">
@@ -1264,7 +1193,7 @@
         <v>UNIT-025</v>
       </c>
       <c r="C26" t="str">
-        <v>Domain Data Models</v>
+        <v>Article Model - Unit Domain</v>
       </c>
       <c r="D26" t="str">
         <v>01_domain_models.test.js</v>
@@ -1276,10 +1205,10 @@
         <v>PASS</v>
       </c>
       <c r="G26">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H26" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="27">
@@ -1290,7 +1219,7 @@
         <v>UNIT-026</v>
       </c>
       <c r="C27" t="str">
-        <v>Domain Data Models</v>
+        <v>Article Model - Unit Domain</v>
       </c>
       <c r="D27" t="str">
         <v>01_domain_models.test.js</v>
@@ -1302,10 +1231,10 @@
         <v>PASS</v>
       </c>
       <c r="G27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="28">
@@ -1316,7 +1245,7 @@
         <v>UNIT-027</v>
       </c>
       <c r="C28" t="str">
-        <v>Domain Data Models</v>
+        <v>Tooth Chart Model Unit Domain</v>
       </c>
       <c r="D28" t="str">
         <v>01_domain_models.test.js</v>
@@ -1328,10 +1257,10 @@
         <v>PASS</v>
       </c>
       <c r="G28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H28" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="29">
@@ -1342,7 +1271,7 @@
         <v>UNIT-028</v>
       </c>
       <c r="C29" t="str">
-        <v>Domain Data Models</v>
+        <v>Tooth Chart Model Unit Domain</v>
       </c>
       <c r="D29" t="str">
         <v>01_domain_models.test.js</v>
@@ -1354,10 +1283,10 @@
         <v>PASS</v>
       </c>
       <c r="G29">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H29" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="30">
@@ -1368,7 +1297,7 @@
         <v>UNIT-029</v>
       </c>
       <c r="C30" t="str">
-        <v>Domain Data Models</v>
+        <v>Tooth Surface Code Unit Domain</v>
       </c>
       <c r="D30" t="str">
         <v>01_domain_models.test.js</v>
@@ -1380,10 +1309,10 @@
         <v>PASS</v>
       </c>
       <c r="G30">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H30" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="31">
@@ -1394,7 +1323,7 @@
         <v>UNIT-030</v>
       </c>
       <c r="C31" t="str">
-        <v>Domain Data Models</v>
+        <v>Patient Medical Alert Unit Domain</v>
       </c>
       <c r="D31" t="str">
         <v>01_domain_models.test.js</v>
@@ -1406,10 +1335,10 @@
         <v>PASS</v>
       </c>
       <c r="G31">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H31" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="32">
@@ -1420,7 +1349,7 @@
         <v>UNIT-031</v>
       </c>
       <c r="C32" t="str">
-        <v>Domain Data Models</v>
+        <v>Allergic Reaction Code Unit Domain</v>
       </c>
       <c r="D32" t="str">
         <v>01_domain_models.test.js</v>
@@ -1432,10 +1361,10 @@
         <v>PASS</v>
       </c>
       <c r="G32">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H32" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="33">
@@ -1446,7 +1375,7 @@
         <v>UNIT-032</v>
       </c>
       <c r="C33" t="str">
-        <v>Domain Data Models</v>
+        <v>Doctor Weekly Schedule Unit Domain</v>
       </c>
       <c r="D33" t="str">
         <v>01_domain_models.test.js</v>
@@ -1458,10 +1387,10 @@
         <v>PASS</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H33" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="34">
@@ -1472,7 +1401,7 @@
         <v>UNIT-033</v>
       </c>
       <c r="C34" t="str">
-        <v>Domain Data Models</v>
+        <v>Doctor Vacation Exclusion Unit Domain</v>
       </c>
       <c r="D34" t="str">
         <v>01_domain_models.test.js</v>
@@ -1484,10 +1413,10 @@
         <v>PASS</v>
       </c>
       <c r="G34">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H34" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="35">
@@ -1498,7 +1427,7 @@
         <v>UNIT-034</v>
       </c>
       <c r="C35" t="str">
-        <v>Domain Data Models</v>
+        <v>Clinic Operational Status Unit Domain</v>
       </c>
       <c r="D35" t="str">
         <v>01_domain_models.test.js</v>
@@ -1510,10 +1439,10 @@
         <v>PASS</v>
       </c>
       <c r="G35">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H35" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="36">
@@ -1524,7 +1453,7 @@
         <v>UNIT-035</v>
       </c>
       <c r="C36" t="str">
-        <v>Domain Data Models</v>
+        <v>Patient Age Calculation Unit Domain</v>
       </c>
       <c r="D36" t="str">
         <v>01_domain_models.test.js</v>
@@ -1539,7 +1468,7 @@
         <v>6</v>
       </c>
       <c r="H36" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="37">
@@ -1550,7 +1479,7 @@
         <v>UNIT-036</v>
       </c>
       <c r="C37" t="str">
-        <v>Domain Data Models</v>
+        <v>Patient Pediatric Category Unit Domain</v>
       </c>
       <c r="D37" t="str">
         <v>01_domain_models.test.js</v>
@@ -1565,7 +1494,7 @@
         <v>9</v>
       </c>
       <c r="H37" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="38">
@@ -1576,7 +1505,7 @@
         <v>UNIT-037</v>
       </c>
       <c r="C38" t="str">
-        <v>Domain Data Models</v>
+        <v>Patient Geriatric Category Unit Domain</v>
       </c>
       <c r="D38" t="str">
         <v>01_domain_models.test.js</v>
@@ -1588,10 +1517,10 @@
         <v>PASS</v>
       </c>
       <c r="G38">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H38" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="39">
@@ -1602,7 +1531,7 @@
         <v>UNIT-038</v>
       </c>
       <c r="C39" t="str">
-        <v>Domain Data Models</v>
+        <v>Clinical Diagnostic Code Unit Domain</v>
       </c>
       <c r="D39" t="str">
         <v>01_domain_models.test.js</v>
@@ -1614,10 +1543,10 @@
         <v>PASS</v>
       </c>
       <c r="G39">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H39" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="40">
@@ -1628,7 +1557,7 @@
         <v>UNIT-039</v>
       </c>
       <c r="C40" t="str">
-        <v>Domain Data Models</v>
+        <v>Dental Procedure Code Unit Domain</v>
       </c>
       <c r="D40" t="str">
         <v>01_domain_models.test.js</v>
@@ -1640,10 +1569,10 @@
         <v>PASS</v>
       </c>
       <c r="G40">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H40" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="41">
@@ -1654,7 +1583,7 @@
         <v>UNIT-040</v>
       </c>
       <c r="C41" t="str">
-        <v>Domain Data Models</v>
+        <v>Insurance Copay Percentage Unit Domain</v>
       </c>
       <c r="D41" t="str">
         <v>01_domain_models.test.js</v>
@@ -1669,7 +1598,7 @@
         <v>3</v>
       </c>
       <c r="H41" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="42">
@@ -1680,7 +1609,7 @@
         <v>UNIT-041</v>
       </c>
       <c r="C42" t="str">
-        <v>Domain Data Models</v>
+        <v>Telehealth Call Session Unit Domain</v>
       </c>
       <c r="D42" t="str">
         <v>01_domain_models.test.js</v>
@@ -1692,10 +1621,10 @@
         <v>PASS</v>
       </c>
       <c r="G42">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H42" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="43">
@@ -1706,7 +1635,7 @@
         <v>UNIT-042</v>
       </c>
       <c r="C43" t="str">
-        <v>Domain Data Models</v>
+        <v>DICOM Patient Anonymization Unit Domain</v>
       </c>
       <c r="D43" t="str">
         <v>01_domain_models.test.js</v>
@@ -1718,10 +1647,10 @@
         <v>PASS</v>
       </c>
       <c r="G43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H43" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="44">
@@ -1732,7 +1661,7 @@
         <v>UNIT-043</v>
       </c>
       <c r="C44" t="str">
-        <v>Domain Data Models</v>
+        <v>Deep Link Routing Unit Domain</v>
       </c>
       <c r="D44" t="str">
         <v>01_domain_models.test.js</v>
@@ -1747,7 +1676,7 @@
         <v>8</v>
       </c>
       <c r="H44" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="45">
@@ -1758,7 +1687,7 @@
         <v>UNIT-044</v>
       </c>
       <c r="C45" t="str">
-        <v>Domain Data Models</v>
+        <v>System Telemetry Log Unit Domain</v>
       </c>
       <c r="D45" t="str">
         <v>01_domain_models.test.js</v>
@@ -1770,10 +1699,10 @@
         <v>PASS</v>
       </c>
       <c r="G45">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H45" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="46">
@@ -1784,7 +1713,7 @@
         <v>UNIT-045</v>
       </c>
       <c r="C46" t="str">
-        <v>Domain Data Models</v>
+        <v>User Role Permission Unit Domain</v>
       </c>
       <c r="D46" t="str">
         <v>01_domain_models.test.js</v>
@@ -1796,10 +1725,10 @@
         <v>PASS</v>
       </c>
       <c r="G46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H46" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="47">
@@ -1810,7 +1739,7 @@
         <v>UNIT-046</v>
       </c>
       <c r="C47" t="str">
-        <v>Domain Data Models</v>
+        <v>JWT Access Token Unit Domain</v>
       </c>
       <c r="D47" t="str">
         <v>01_domain_models.test.js</v>
@@ -1822,10 +1751,10 @@
         <v>PASS</v>
       </c>
       <c r="G47">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H47" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="48">
@@ -1836,7 +1765,7 @@
         <v>UNIT-047</v>
       </c>
       <c r="C48" t="str">
-        <v>Domain Data Models</v>
+        <v>JWT Refresh Token Unit Domain</v>
       </c>
       <c r="D48" t="str">
         <v>01_domain_models.test.js</v>
@@ -1848,10 +1777,10 @@
         <v>PASS</v>
       </c>
       <c r="G48">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H48" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="49">
@@ -1862,7 +1791,7 @@
         <v>UNIT-048</v>
       </c>
       <c r="C49" t="str">
-        <v>Domain Data Models</v>
+        <v>Dynamic Notification Template Unit Domain</v>
       </c>
       <c r="D49" t="str">
         <v>01_domain_models.test.js</v>
@@ -1874,10 +1803,10 @@
         <v>PASS</v>
       </c>
       <c r="G49">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H49" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="50">
@@ -1888,7 +1817,7 @@
         <v>UNIT-049</v>
       </c>
       <c r="C50" t="str">
-        <v>Domain Data Models</v>
+        <v>Pagination Cursor Encoder/Decoder Unit Domain</v>
       </c>
       <c r="D50" t="str">
         <v>01_domain_models.test.js</v>
@@ -1900,10 +1829,10 @@
         <v>PASS</v>
       </c>
       <c r="G50">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H50" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="51">
@@ -1914,7 +1843,7 @@
         <v>UNIT-050</v>
       </c>
       <c r="C51" t="str">
-        <v>Domain Data Models</v>
+        <v>Sorting Field Order Unit Domain</v>
       </c>
       <c r="D51" t="str">
         <v>01_domain_models.test.js</v>
@@ -1926,10 +1855,10 @@
         <v>PASS</v>
       </c>
       <c r="G51">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H51" t="str">
-        <v>2026-08-06T05:04:35.745Z</v>
+        <v>2026-08-06T05:06:54.899Z</v>
       </c>
     </row>
     <row r="52">
@@ -1940,7 +1869,7 @@
         <v>UNIT-051</v>
       </c>
       <c r="C52" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Triage Risk Score Unit Domain</v>
       </c>
       <c r="D52" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -1952,10 +1881,10 @@
         <v>PASS</v>
       </c>
       <c r="G52">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H52" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="53">
@@ -1966,7 +1895,7 @@
         <v>UNIT-052</v>
       </c>
       <c r="C53" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>FDI To Universal Unit Domain</v>
       </c>
       <c r="D53" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -1978,10 +1907,10 @@
         <v>PASS</v>
       </c>
       <c r="G53">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H53" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="54">
@@ -1992,7 +1921,7 @@
         <v>UNIT-053</v>
       </c>
       <c r="C54" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Universal To FDI Unit Domain</v>
       </c>
       <c r="D54" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2004,10 +1933,10 @@
         <v>PASS</v>
       </c>
       <c r="G54">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H54" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="55">
@@ -2018,7 +1947,7 @@
         <v>UNIT-054</v>
       </c>
       <c r="C55" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Gum Bleeding Index Unit Domain</v>
       </c>
       <c r="D55" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2030,10 +1959,10 @@
         <v>PASS</v>
       </c>
       <c r="G55">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H55" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="56">
@@ -2044,7 +1973,7 @@
         <v>UNIT-055</v>
       </c>
       <c r="C56" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Plaque Accumulation Coverage Unit Domain</v>
       </c>
       <c r="D56" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2056,10 +1985,10 @@
         <v>PASS</v>
       </c>
       <c r="G56">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H56" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="57">
@@ -2070,7 +1999,7 @@
         <v>UNIT-056</v>
       </c>
       <c r="C57" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Periodontal Pocket Depth Unit Domain</v>
       </c>
       <c r="D57" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2082,10 +2011,10 @@
         <v>PASS</v>
       </c>
       <c r="G57">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H57" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="58">
@@ -2096,7 +2025,7 @@
         <v>UNIT-057</v>
       </c>
       <c r="C58" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Carious Lesion Depth Unit Domain</v>
       </c>
       <c r="D58" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2108,10 +2037,10 @@
         <v>PASS</v>
       </c>
       <c r="G58">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H58" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="59">
@@ -2122,7 +2051,7 @@
         <v>UNIT-058</v>
       </c>
       <c r="C59" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Enamel Erosion Severity Unit Domain</v>
       </c>
       <c r="D59" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2134,10 +2063,10 @@
         <v>PASS</v>
       </c>
       <c r="G59">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H59" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="60">
@@ -2148,7 +2077,7 @@
         <v>UNIT-059</v>
       </c>
       <c r="C60" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Wisdom Tooth Impaction Unit Domain</v>
       </c>
       <c r="D60" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2160,10 +2089,10 @@
         <v>PASS</v>
       </c>
       <c r="G60">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H60" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="61">
@@ -2174,7 +2103,7 @@
         <v>UNIT-060</v>
       </c>
       <c r="C61" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>TMJ Disorder Severity Unit Domain</v>
       </c>
       <c r="D61" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2186,10 +2115,10 @@
         <v>PASS</v>
       </c>
       <c r="G61">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H61" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="62">
@@ -2200,7 +2129,7 @@
         <v>UNIT-061</v>
       </c>
       <c r="C62" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Dental Sensitivity Temperature Unit Domain</v>
       </c>
       <c r="D62" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2212,10 +2141,10 @@
         <v>PASS</v>
       </c>
       <c r="G62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H62" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="63">
@@ -2226,7 +2155,7 @@
         <v>UNIT-062</v>
       </c>
       <c r="C63" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Emergency Triage Escalation Unit Domain</v>
       </c>
       <c r="D63" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2238,10 +2167,10 @@
         <v>PASS</v>
       </c>
       <c r="G63">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H63" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="64">
@@ -2252,7 +2181,7 @@
         <v>UNIT-063</v>
       </c>
       <c r="C64" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Differential Diagnosis Likelihood Unit Domain</v>
       </c>
       <c r="D64" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2264,10 +2193,10 @@
         <v>PASS</v>
       </c>
       <c r="G64">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H64" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="65">
@@ -2278,7 +2207,7 @@
         <v>UNIT-064</v>
       </c>
       <c r="C65" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Pediatric Teething Symptoms Unit Domain</v>
       </c>
       <c r="D65" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2290,10 +2219,10 @@
         <v>PASS</v>
       </c>
       <c r="G65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H65" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="66">
@@ -2304,7 +2233,7 @@
         <v>UNIT-065</v>
       </c>
       <c r="C66" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Orthodontic Alignment Malocclusion Unit Domain</v>
       </c>
       <c r="D66" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2316,10 +2245,10 @@
         <v>PASS</v>
       </c>
       <c r="G66">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H66" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="67">
@@ -2330,7 +2259,7 @@
         <v>UNIT-066</v>
       </c>
       <c r="C67" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Bruxism Tooth Wear Unit Domain</v>
       </c>
       <c r="D67" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2342,10 +2271,10 @@
         <v>PASS</v>
       </c>
       <c r="G67">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H67" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="68">
@@ -2356,7 +2285,7 @@
         <v>UNIT-067</v>
       </c>
       <c r="C68" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Halitosis Volatile Sulfur Unit Domain</v>
       </c>
       <c r="D68" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2368,10 +2297,10 @@
         <v>PASS</v>
       </c>
       <c r="G68">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H68" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="69">
@@ -2382,7 +2311,7 @@
         <v>UNIT-068</v>
       </c>
       <c r="C69" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Dry Mouth Salivary Unit Domain</v>
       </c>
       <c r="D69" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2394,10 +2323,10 @@
         <v>PASS</v>
       </c>
       <c r="G69">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H69" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="70">
@@ -2408,7 +2337,7 @@
         <v>UNIT-069</v>
       </c>
       <c r="C70" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Canker Sore Vs Unit Domain</v>
       </c>
       <c r="D70" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2420,10 +2349,10 @@
         <v>PASS</v>
       </c>
       <c r="G70">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H70" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="71">
@@ -2434,7 +2363,7 @@
         <v>UNIT-070</v>
       </c>
       <c r="C71" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Salivary Gland Blockage Unit Domain</v>
       </c>
       <c r="D71" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2446,10 +2375,10 @@
         <v>PASS</v>
       </c>
       <c r="G71">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H71" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="72">
@@ -2460,7 +2389,7 @@
         <v>UNIT-071</v>
       </c>
       <c r="C72" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Dental Trauma Severity Unit Domain</v>
       </c>
       <c r="D72" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2472,10 +2401,10 @@
         <v>PASS</v>
       </c>
       <c r="G72">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H72" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="73">
@@ -2486,7 +2415,7 @@
         <v>UNIT-072</v>
       </c>
       <c r="C73" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Root Canal Infection Unit Domain</v>
       </c>
       <c r="D73" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2498,10 +2427,10 @@
         <v>PASS</v>
       </c>
       <c r="G73">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H73" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="74">
@@ -2512,7 +2441,7 @@
         <v>UNIT-073</v>
       </c>
       <c r="C74" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Crown Falling Off Unit Domain</v>
       </c>
       <c r="D74" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2524,10 +2453,10 @@
         <v>PASS</v>
       </c>
       <c r="G74">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H74" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="75">
@@ -2538,7 +2467,7 @@
         <v>UNIT-074</v>
       </c>
       <c r="C75" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Extraction Socket Dry Unit Domain</v>
       </c>
       <c r="D75" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2550,10 +2479,10 @@
         <v>PASS</v>
       </c>
       <c r="G75">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H75" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="76">
@@ -2564,7 +2493,7 @@
         <v>UNIT-075</v>
       </c>
       <c r="C76" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Dental Whitening Sensitivity Unit Domain</v>
       </c>
       <c r="D76" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2576,10 +2505,10 @@
         <v>PASS</v>
       </c>
       <c r="G76">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H76" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="77">
@@ -2590,7 +2519,7 @@
         <v>UNIT-076</v>
       </c>
       <c r="C77" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Lip Cracking Cheilitis Unit Domain</v>
       </c>
       <c r="D77" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2602,10 +2531,10 @@
         <v>PASS</v>
       </c>
       <c r="G77">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H77" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="78">
@@ -2616,7 +2545,7 @@
         <v>UNIT-077</v>
       </c>
       <c r="C78" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Tongue Lesion Color Unit Domain</v>
       </c>
       <c r="D78" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2628,10 +2557,10 @@
         <v>PASS</v>
       </c>
       <c r="G78">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H78" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="79">
@@ -2642,7 +2571,7 @@
         <v>UNIT-078</v>
       </c>
       <c r="C79" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Metallic Taste Heavy Unit Domain</v>
       </c>
       <c r="D79" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2657,7 +2586,7 @@
         <v>2</v>
       </c>
       <c r="H79" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="80">
@@ -2668,7 +2597,7 @@
         <v>UNIT-079</v>
       </c>
       <c r="C80" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Dysphagia Swallowing Obstruction Unit Domain</v>
       </c>
       <c r="D80" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2680,10 +2609,10 @@
         <v>PASS</v>
       </c>
       <c r="G80">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H80" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="81">
@@ -2694,7 +2623,7 @@
         <v>UNIT-080</v>
       </c>
       <c r="C81" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Sinus Pressure Related Unit Domain</v>
       </c>
       <c r="D81" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2706,10 +2635,10 @@
         <v>PASS</v>
       </c>
       <c r="G81">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H81" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="82">
@@ -2720,7 +2649,7 @@
         <v>UNIT-081</v>
       </c>
       <c r="C82" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Pregnancy Gingivitis Hormonal Unit Domain</v>
       </c>
       <c r="D82" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2732,10 +2661,10 @@
         <v>PASS</v>
       </c>
       <c r="G82">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H82" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="83">
@@ -2746,7 +2675,7 @@
         <v>UNIT-082</v>
       </c>
       <c r="C83" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Diabetes Periodontal Disease Unit Domain</v>
       </c>
       <c r="D83" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2758,10 +2687,10 @@
         <v>PASS</v>
       </c>
       <c r="G83">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H83" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="84">
@@ -2772,7 +2701,7 @@
         <v>UNIT-083</v>
       </c>
       <c r="C84" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Smoker Nicotine Staining Unit Domain</v>
       </c>
       <c r="D84" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2784,10 +2713,10 @@
         <v>PASS</v>
       </c>
       <c r="G84">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H84" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="85">
@@ -2798,7 +2727,7 @@
         <v>UNIT-084</v>
       </c>
       <c r="C85" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Post-Op Infection Temperature Unit Domain</v>
       </c>
       <c r="D85" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2810,10 +2739,10 @@
         <v>PASS</v>
       </c>
       <c r="G85">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H85" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="86">
@@ -2824,7 +2753,7 @@
         <v>UNIT-085</v>
       </c>
       <c r="C86" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Dentural Stomatitis Soreness Unit Domain</v>
       </c>
       <c r="D86" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2836,10 +2765,10 @@
         <v>PASS</v>
       </c>
       <c r="G86">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H86" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="87">
@@ -2850,7 +2779,7 @@
         <v>UNIT-086</v>
       </c>
       <c r="C87" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Orthodontic Wire Abrasion Unit Domain</v>
       </c>
       <c r="D87" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2862,10 +2791,10 @@
         <v>PASS</v>
       </c>
       <c r="G87">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H87" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="88">
@@ -2876,7 +2805,7 @@
         <v>UNIT-087</v>
       </c>
       <c r="C88" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Dental Caries Risk Unit Domain</v>
       </c>
       <c r="D88" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2891,7 +2820,7 @@
         <v>3</v>
       </c>
       <c r="H88" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="89">
@@ -2902,7 +2831,7 @@
         <v>UNIT-088</v>
       </c>
       <c r="C89" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Fluorosis Staining Classification Unit Domain</v>
       </c>
       <c r="D89" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2914,10 +2843,10 @@
         <v>PASS</v>
       </c>
       <c r="G89">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H89" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="90">
@@ -2928,7 +2857,7 @@
         <v>UNIT-089</v>
       </c>
       <c r="C90" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Dental Erosion PH Unit Domain</v>
       </c>
       <c r="D90" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2940,10 +2869,10 @@
         <v>PASS</v>
       </c>
       <c r="G90">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H90" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="91">
@@ -2954,7 +2883,7 @@
         <v>UNIT-090</v>
       </c>
       <c r="C91" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Mouth Breathing Airway Unit Domain</v>
       </c>
       <c r="D91" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2966,10 +2895,10 @@
         <v>PASS</v>
       </c>
       <c r="G91">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H91" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="92">
@@ -2980,7 +2909,7 @@
         <v>UNIT-091</v>
       </c>
       <c r="C92" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Ear Pain Radiation Unit Domain</v>
       </c>
       <c r="D92" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -2992,10 +2921,10 @@
         <v>PASS</v>
       </c>
       <c r="G92">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H92" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="93">
@@ -3006,7 +2935,7 @@
         <v>UNIT-092</v>
       </c>
       <c r="C93" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Auto-save Progress State Unit Domain</v>
       </c>
       <c r="D93" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -3021,7 +2950,7 @@
         <v>11</v>
       </c>
       <c r="H93" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="94">
@@ -3032,7 +2961,7 @@
         <v>UNIT-093</v>
       </c>
       <c r="C94" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Diagnostic Certainty Confidence Unit Domain</v>
       </c>
       <c r="D94" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -3044,10 +2973,10 @@
         <v>PASS</v>
       </c>
       <c r="G94">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H94" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="95">
@@ -3058,7 +2987,7 @@
         <v>UNIT-094</v>
       </c>
       <c r="C95" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Severity Score Normalized Unit Domain</v>
       </c>
       <c r="D95" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -3070,10 +2999,10 @@
         <v>PASS</v>
       </c>
       <c r="G95">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H95" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="96">
@@ -3084,7 +3013,7 @@
         <v>UNIT-095</v>
       </c>
       <c r="C96" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Risk Factor Weighted Unit Domain</v>
       </c>
       <c r="D96" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -3096,10 +3025,10 @@
         <v>PASS</v>
       </c>
       <c r="G96">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H96" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="97">
@@ -3110,7 +3039,7 @@
         <v>UNIT-096</v>
       </c>
       <c r="C97" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Emergency Triage Red Unit Domain</v>
       </c>
       <c r="D97" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -3122,10 +3051,10 @@
         <v>PASS</v>
       </c>
       <c r="G97">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H97" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="98">
@@ -3136,7 +3065,7 @@
         <v>UNIT-097</v>
       </c>
       <c r="C98" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Primary Vs Secondary Unit Domain</v>
       </c>
       <c r="D98" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -3148,10 +3077,10 @@
         <v>PASS</v>
       </c>
       <c r="G98">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H98" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="99">
@@ -3162,7 +3091,7 @@
         <v>UNIT-098</v>
       </c>
       <c r="C99" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Chronic Vs Acute Unit Domain</v>
       </c>
       <c r="D99" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -3174,10 +3103,10 @@
         <v>PASS</v>
       </c>
       <c r="G99">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H99" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="100">
@@ -3188,7 +3117,7 @@
         <v>UNIT-099</v>
       </c>
       <c r="C100" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Symptom Duration Unit Unit Domain</v>
       </c>
       <c r="D100" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -3200,10 +3129,10 @@
         <v>PASS</v>
       </c>
       <c r="G100">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H100" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="101">
@@ -3214,7 +3143,7 @@
         <v>UNIT-100</v>
       </c>
       <c r="C101" t="str">
-        <v>Diagnostic Rule Engine</v>
+        <v>Clinical Diagnostic Report Unit Domain</v>
       </c>
       <c r="D101" t="str">
         <v>02_diagnostic_engine.test.js</v>
@@ -3226,10 +3155,10 @@
         <v>PASS</v>
       </c>
       <c r="G101">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H101" t="str">
-        <v>2026-08-06T05:04:35.749Z</v>
+        <v>2026-08-06T05:06:54.903Z</v>
       </c>
     </row>
     <row r="102">
@@ -3240,7 +3169,7 @@
         <v>UNIT-101</v>
       </c>
       <c r="C102" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>BPE Tokenizer Word Unit Domain</v>
       </c>
       <c r="D102" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -3252,10 +3181,10 @@
         <v>PASS</v>
       </c>
       <c r="G102">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H102" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="103">
@@ -3266,7 +3195,7 @@
         <v>UNIT-102</v>
       </c>
       <c r="C103" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>System Prompt Persona Unit Domain</v>
       </c>
       <c r="D103" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -3278,10 +3207,10 @@
         <v>PASS</v>
       </c>
       <c r="G103">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H103" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="104">
@@ -3292,7 +3221,7 @@
         <v>UNIT-103</v>
       </c>
       <c r="C104" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>LLM JSON Output Unit Domain</v>
       </c>
       <c r="D104" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -3304,10 +3233,10 @@
         <v>PASS</v>
       </c>
       <c r="G104">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H104" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="105">
@@ -3318,7 +3247,7 @@
         <v>UNIT-104</v>
       </c>
       <c r="C105" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Extract Bounding Boxes Unit Domain</v>
       </c>
       <c r="D105" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -3330,10 +3259,10 @@
         <v>PASS</v>
       </c>
       <c r="G105">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H105" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="106">
@@ -3344,7 +3273,7 @@
         <v>UNIT-105</v>
       </c>
       <c r="C106" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Extract Clinical Findings Unit Domain</v>
       </c>
       <c r="D106" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -3356,10 +3285,10 @@
         <v>PASS</v>
       </c>
       <c r="G106">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H106" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="107">
@@ -3370,7 +3299,7 @@
         <v>UNIT-106</v>
       </c>
       <c r="C107" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Sanitize Unsafe HTML Unit Domain</v>
       </c>
       <c r="D107" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -3382,10 +3311,10 @@
         <v>PASS</v>
       </c>
       <c r="G107">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H107" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="108">
@@ -3396,7 +3325,7 @@
         <v>UNIT-107</v>
       </c>
       <c r="C108" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Convert Markdown Bullets Unit Domain</v>
       </c>
       <c r="D108" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -3411,7 +3340,7 @@
         <v>9</v>
       </c>
       <c r="H108" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="109">
@@ -3422,7 +3351,7 @@
         <v>UNIT-108</v>
       </c>
       <c r="C109" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Parse AI Dental Unit Domain</v>
       </c>
       <c r="D109" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -3434,10 +3363,10 @@
         <v>PASS</v>
       </c>
       <c r="G109">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H109" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="110">
@@ -3448,7 +3377,7 @@
         <v>UNIT-109</v>
       </c>
       <c r="C110" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Truncate Chat Context Unit Domain</v>
       </c>
       <c r="D110" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -3460,10 +3389,10 @@
         <v>PASS</v>
       </c>
       <c r="G110">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H110" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="111">
@@ -3474,7 +3403,7 @@
         <v>UNIT-110</v>
       </c>
       <c r="C111" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Sliding Context Window Unit Domain</v>
       </c>
       <c r="D111" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -3486,10 +3415,10 @@
         <v>PASS</v>
       </c>
       <c r="G111">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H111" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="112">
@@ -3500,7 +3429,7 @@
         <v>UNIT-111</v>
       </c>
       <c r="C112" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Calculate Token Cost Unit Domain</v>
       </c>
       <c r="D112" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -3512,10 +3441,10 @@
         <v>PASS</v>
       </c>
       <c r="G112">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H112" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="113">
@@ -3526,7 +3455,7 @@
         <v>UNIT-112</v>
       </c>
       <c r="C113" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Medical Terminology Glossary Unit Domain</v>
       </c>
       <c r="D113" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -3538,10 +3467,10 @@
         <v>PASS</v>
       </c>
       <c r="G113">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H113" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="114">
@@ -3552,7 +3481,7 @@
         <v>UNIT-113</v>
       </c>
       <c r="C114" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Detect Emergency Keywords Unit Domain</v>
       </c>
       <c r="D114" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -3564,10 +3493,10 @@
         <v>PASS</v>
       </c>
       <c r="G114">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H114" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="115">
@@ -3578,7 +3507,7 @@
         <v>UNIT-114</v>
       </c>
       <c r="C115" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>System Disclaimer Footer Unit Domain</v>
       </c>
       <c r="D115" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -3593,7 +3522,7 @@
         <v>9</v>
       </c>
       <c r="H115" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="116">
@@ -3604,7 +3533,7 @@
         <v>UNIT-115</v>
       </c>
       <c r="C116" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Parse Structured Diagnosis Unit Domain</v>
       </c>
       <c r="D116" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -3616,10 +3545,10 @@
         <v>PASS</v>
       </c>
       <c r="G116">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H116" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="117">
@@ -3630,7 +3559,7 @@
         <v>UNIT-116</v>
       </c>
       <c r="C117" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Format Clinical Findings Unit Domain</v>
       </c>
       <c r="D117" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -3642,10 +3571,10 @@
         <v>PASS</v>
       </c>
       <c r="G117">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H117" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="118">
@@ -3656,7 +3585,7 @@
         <v>UNIT-117</v>
       </c>
       <c r="C118" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Extract Recommended Dental Unit Domain</v>
       </c>
       <c r="D118" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -3668,10 +3597,10 @@
         <v>PASS</v>
       </c>
       <c r="G118">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H118" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="119">
@@ -3682,7 +3611,7 @@
         <v>UNIT-118</v>
       </c>
       <c r="C119" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Filter Out PII Unit Domain</v>
       </c>
       <c r="D119" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -3694,10 +3623,10 @@
         <v>PASS</v>
       </c>
       <c r="G119">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H119" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="120">
@@ -3708,7 +3637,7 @@
         <v>UNIT-119</v>
       </c>
       <c r="C120" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Sanitize Patient Name Unit Domain</v>
       </c>
       <c r="D120" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -3720,10 +3649,10 @@
         <v>PASS</v>
       </c>
       <c r="G120">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H120" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="121">
@@ -3734,7 +3663,7 @@
         <v>UNIT-120</v>
       </c>
       <c r="C121" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Parse Dental Tooth Unit Domain</v>
       </c>
       <c r="D121" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -3746,10 +3675,10 @@
         <v>PASS</v>
       </c>
       <c r="G121">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H121" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="122">
@@ -3760,7 +3689,7 @@
         <v>UNIT-121</v>
       </c>
       <c r="C122" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Extract Urgency Level Unit Domain</v>
       </c>
       <c r="D122" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -3772,10 +3701,10 @@
         <v>PASS</v>
       </c>
       <c r="G122">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H122" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="123">
@@ -3786,7 +3715,7 @@
         <v>UNIT-122</v>
       </c>
       <c r="C123" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Calculate Response Sentiment Unit Domain</v>
       </c>
       <c r="D123" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -3798,10 +3727,10 @@
         <v>PASS</v>
       </c>
       <c r="G123">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H123" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="124">
@@ -3812,7 +3741,7 @@
         <v>UNIT-123</v>
       </c>
       <c r="C124" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Validate LLM Response Unit Domain</v>
       </c>
       <c r="D124" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -3824,10 +3753,10 @@
         <v>PASS</v>
       </c>
       <c r="G124">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H124" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="125">
@@ -3838,7 +3767,7 @@
         <v>UNIT-124</v>
       </c>
       <c r="C125" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Fallback Error Response Unit Domain</v>
       </c>
       <c r="D125" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -3850,10 +3779,10 @@
         <v>PASS</v>
       </c>
       <c r="G125">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H125" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="126">
@@ -3864,7 +3793,7 @@
         <v>UNIT-125</v>
       </c>
       <c r="C126" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Retry Prompt Builder Unit Domain</v>
       </c>
       <c r="D126" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -3876,10 +3805,10 @@
         <v>PASS</v>
       </c>
       <c r="G126">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H126" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="127">
@@ -3890,7 +3819,7 @@
         <v>UNIT-126</v>
       </c>
       <c r="C127" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Remove Code Fences Unit Domain</v>
       </c>
       <c r="D127" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -3902,10 +3831,10 @@
         <v>PASS</v>
       </c>
       <c r="G127">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H127" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="128">
@@ -3916,7 +3845,7 @@
         <v>UNIT-127</v>
       </c>
       <c r="C128" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Extract Medication Name Unit Domain</v>
       </c>
       <c r="D128" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -3928,10 +3857,10 @@
         <v>PASS</v>
       </c>
       <c r="G128">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H128" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="129">
@@ -3942,7 +3871,7 @@
         <v>UNIT-128</v>
       </c>
       <c r="C129" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Detect Medical Contraindication Unit Domain</v>
       </c>
       <c r="D129" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -3954,10 +3883,10 @@
         <v>PASS</v>
       </c>
       <c r="G129">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H129" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="130">
@@ -3968,7 +3897,7 @@
         <v>UNIT-129</v>
       </c>
       <c r="C130" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Parse Follow-up Questions Unit Domain</v>
       </c>
       <c r="D130" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -3980,10 +3909,10 @@
         <v>PASS</v>
       </c>
       <c r="G130">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H130" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="131">
@@ -3994,7 +3923,7 @@
         <v>UNIT-130</v>
       </c>
       <c r="C131" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Highlight Critical Emergency Unit Domain</v>
       </c>
       <c r="D131" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -4006,10 +3935,10 @@
         <v>PASS</v>
       </c>
       <c r="G131">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H131" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="132">
@@ -4020,7 +3949,7 @@
         <v>UNIT-131</v>
       </c>
       <c r="C132" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Translate Clinical Terms Unit Domain</v>
       </c>
       <c r="D132" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -4035,7 +3964,7 @@
         <v>11</v>
       </c>
       <c r="H132" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="133">
@@ -4046,7 +3975,7 @@
         <v>UNIT-132</v>
       </c>
       <c r="C133" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Count Syllables For Unit Domain</v>
       </c>
       <c r="D133" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -4058,10 +3987,10 @@
         <v>PASS</v>
       </c>
       <c r="G133">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H133" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="134">
@@ -4072,7 +4001,7 @@
         <v>UNIT-133</v>
       </c>
       <c r="C134" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Flesch-Kincaid Reading Ease Unit Domain</v>
       </c>
       <c r="D134" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -4084,10 +4013,10 @@
         <v>PASS</v>
       </c>
       <c r="G134">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H134" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="135">
@@ -4098,7 +4027,7 @@
         <v>UNIT-134</v>
       </c>
       <c r="C135" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Format Time Slot Unit Domain</v>
       </c>
       <c r="D135" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -4110,10 +4039,10 @@
         <v>PASS</v>
       </c>
       <c r="G135">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H135" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="136">
@@ -4124,7 +4053,7 @@
         <v>UNIT-135</v>
       </c>
       <c r="C136" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Filter Unsupported Medical Unit Domain</v>
       </c>
       <c r="D136" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -4136,10 +4065,10 @@
         <v>PASS</v>
       </c>
       <c r="G136">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H136" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="137">
@@ -4150,7 +4079,7 @@
         <v>UNIT-136</v>
       </c>
       <c r="C137" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Strip LLM Hallucinated Unit Domain</v>
       </c>
       <c r="D137" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -4162,10 +4091,10 @@
         <v>PASS</v>
       </c>
       <c r="G137">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H137" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="138">
@@ -4176,7 +4105,7 @@
         <v>UNIT-137</v>
       </c>
       <c r="C138" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Parse Multi-Choice Symptom Unit Domain</v>
       </c>
       <c r="D138" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -4188,10 +4117,10 @@
         <v>PASS</v>
       </c>
       <c r="G138">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H138" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="139">
@@ -4202,7 +4131,7 @@
         <v>UNIT-138</v>
       </c>
       <c r="C139" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Format X-Ray Findings Unit Domain</v>
       </c>
       <c r="D139" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -4214,10 +4143,10 @@
         <v>PASS</v>
       </c>
       <c r="G139">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H139" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="140">
@@ -4228,7 +4157,7 @@
         <v>UNIT-139</v>
       </c>
       <c r="C140" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Validate System Prompt Unit Domain</v>
       </c>
       <c r="D140" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -4240,10 +4169,10 @@
         <v>PASS</v>
       </c>
       <c r="G140">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H140" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="141">
@@ -4254,7 +4183,7 @@
         <v>UNIT-140</v>
       </c>
       <c r="C141" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Detect Language Code Unit Domain</v>
       </c>
       <c r="D141" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -4266,10 +4195,10 @@
         <v>PASS</v>
       </c>
       <c r="G141">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H141" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="142">
@@ -4280,7 +4209,7 @@
         <v>UNIT-141</v>
       </c>
       <c r="C142" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Construct Pediatric Friendly Unit Domain</v>
       </c>
       <c r="D142" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -4292,10 +4221,10 @@
         <v>PASS</v>
       </c>
       <c r="G142">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H142" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="143">
@@ -4306,7 +4235,7 @@
         <v>UNIT-142</v>
       </c>
       <c r="C143" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Construct Dental Specialist Unit Domain</v>
       </c>
       <c r="D143" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -4318,10 +4247,10 @@
         <v>PASS</v>
       </c>
       <c r="G143">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H143" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="144">
@@ -4332,7 +4261,7 @@
         <v>UNIT-143</v>
       </c>
       <c r="C144" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Construct Emergency Triage Unit Domain</v>
       </c>
       <c r="D144" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -4344,10 +4273,10 @@
         <v>PASS</v>
       </c>
       <c r="G144">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H144" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="145">
@@ -4358,7 +4287,7 @@
         <v>UNIT-144</v>
       </c>
       <c r="C145" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Format Doctor Review Unit Domain</v>
       </c>
       <c r="D145" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -4370,10 +4299,10 @@
         <v>PASS</v>
       </c>
       <c r="G145">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H145" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="146">
@@ -4384,7 +4313,7 @@
         <v>UNIT-145</v>
       </c>
       <c r="C146" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Extract Confidence Percentage Unit Domain</v>
       </c>
       <c r="D146" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -4396,10 +4325,10 @@
         <v>PASS</v>
       </c>
       <c r="G146">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H146" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="147">
@@ -4410,7 +4339,7 @@
         <v>UNIT-146</v>
       </c>
       <c r="C147" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Parse Tooth Surface Unit Domain</v>
       </c>
       <c r="D147" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -4422,10 +4351,10 @@
         <v>PASS</v>
       </c>
       <c r="G147">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H147" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="148">
@@ -4436,7 +4365,7 @@
         <v>UNIT-147</v>
       </c>
       <c r="C148" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Sanitize Emoji Icons Unit Domain</v>
       </c>
       <c r="D148" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -4448,10 +4377,10 @@
         <v>PASS</v>
       </c>
       <c r="G148">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H148" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="149">
@@ -4462,7 +4391,7 @@
         <v>UNIT-148</v>
       </c>
       <c r="C149" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Convert Celsius To Unit Domain</v>
       </c>
       <c r="D149" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -4474,10 +4403,10 @@
         <v>PASS</v>
       </c>
       <c r="G149">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H149" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="150">
@@ -4488,7 +4417,7 @@
         <v>UNIT-149</v>
       </c>
       <c r="C150" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Validate Multi-Modal Image Unit Domain</v>
       </c>
       <c r="D150" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -4500,10 +4429,10 @@
         <v>PASS</v>
       </c>
       <c r="G150">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H150" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="151">
@@ -4514,7 +4443,7 @@
         <v>UNIT-150</v>
       </c>
       <c r="C151" t="str">
-        <v>AI Prompt Tokenizer &amp; Parsers</v>
+        <v>Token Streaming Chunk Unit Domain</v>
       </c>
       <c r="D151" t="str">
         <v>03_ai_prompt_parsers.test.js</v>
@@ -4526,10 +4455,10 @@
         <v>PASS</v>
       </c>
       <c r="G151">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H151" t="str">
-        <v>2026-08-06T05:04:35.752Z</v>
+        <v>2026-08-06T05:06:54.909Z</v>
       </c>
     </row>
     <row r="152">
@@ -4540,7 +4469,7 @@
         <v>UNIT-151</v>
       </c>
       <c r="C152" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Calculate Available Slots Unit Domain</v>
       </c>
       <c r="D152" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -4552,10 +4481,10 @@
         <v>PASS</v>
       </c>
       <c r="G152">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H152" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="153">
@@ -4566,7 +4495,7 @@
         <v>UNIT-152</v>
       </c>
       <c r="C153" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Detect Time Slot Unit Domain</v>
       </c>
       <c r="D153" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -4581,7 +4510,7 @@
         <v>3</v>
       </c>
       <c r="H153" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="154">
@@ -4592,7 +4521,7 @@
         <v>UNIT-153</v>
       </c>
       <c r="C154" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Filter Out Past Unit Domain</v>
       </c>
       <c r="D154" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -4604,10 +4533,10 @@
         <v>PASS</v>
       </c>
       <c r="G154">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H154" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="155">
@@ -4618,7 +4547,7 @@
         <v>UNIT-154</v>
       </c>
       <c r="C155" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Timezone Offset Converter Unit Domain</v>
       </c>
       <c r="D155" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -4630,10 +4559,10 @@
         <v>PASS</v>
       </c>
       <c r="G155">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H155" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="156">
@@ -4644,7 +4573,7 @@
         <v>UNIT-155</v>
       </c>
       <c r="C156" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>ISO 8601 Timestamp Unit Domain</v>
       </c>
       <c r="D156" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -4656,10 +4585,10 @@
         <v>PASS</v>
       </c>
       <c r="G156">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H156" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="157">
@@ -4670,7 +4599,7 @@
         <v>UNIT-156</v>
       </c>
       <c r="C157" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Doctor Lunch Break Unit Domain</v>
       </c>
       <c r="D157" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -4682,10 +4611,10 @@
         <v>PASS</v>
       </c>
       <c r="G157">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H157" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="158">
@@ -4696,7 +4625,7 @@
         <v>UNIT-157</v>
       </c>
       <c r="C158" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Doctor Vacation Date Unit Domain</v>
       </c>
       <c r="D158" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -4708,10 +4637,10 @@
         <v>PASS</v>
       </c>
       <c r="G158">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H158" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="159">
@@ -4722,7 +4651,7 @@
         <v>UNIT-158</v>
       </c>
       <c r="C159" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Calculate Next Available Unit Domain</v>
       </c>
       <c r="D159" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -4737,7 +4666,7 @@
         <v>10</v>
       </c>
       <c r="H159" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="160">
@@ -4748,7 +4677,7 @@
         <v>UNIT-159</v>
       </c>
       <c r="C160" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Appointment Duration Custom Unit Domain</v>
       </c>
       <c r="D160" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -4760,10 +4689,10 @@
         <v>PASS</v>
       </c>
       <c r="G160">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H160" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="161">
@@ -4774,7 +4703,7 @@
         <v>UNIT-160</v>
       </c>
       <c r="C161" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Buffer Time Insertion Unit Domain</v>
       </c>
       <c r="D161" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -4786,10 +4715,10 @@
         <v>PASS</v>
       </c>
       <c r="G161">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H161" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="162">
@@ -4800,7 +4729,7 @@
         <v>UNIT-161</v>
       </c>
       <c r="C162" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Cancellation Fee Percentage Unit Domain</v>
       </c>
       <c r="D162" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -4812,10 +4741,10 @@
         <v>PASS</v>
       </c>
       <c r="G162">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H162" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="163">
@@ -4826,7 +4755,7 @@
         <v>UNIT-162</v>
       </c>
       <c r="C163" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>24-Hour Notice Cancellation Unit Domain</v>
       </c>
       <c r="D163" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -4838,10 +4767,10 @@
         <v>PASS</v>
       </c>
       <c r="G163">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H163" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="164">
@@ -4852,7 +4781,7 @@
         <v>UNIT-163</v>
       </c>
       <c r="C164" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>No-Show Penalty Calculation Unit Domain</v>
       </c>
       <c r="D164" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -4864,10 +4793,10 @@
         <v>PASS</v>
       </c>
       <c r="G164">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H164" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="165">
@@ -4878,7 +4807,7 @@
         <v>UNIT-164</v>
       </c>
       <c r="C165" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Insurance Copay Amount Unit Domain</v>
       </c>
       <c r="D165" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -4890,10 +4819,10 @@
         <v>PASS</v>
       </c>
       <c r="G165">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H165" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="166">
@@ -4904,7 +4833,7 @@
         <v>UNIT-165</v>
       </c>
       <c r="C166" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Insurance Out-of-Pocket Max Unit Domain</v>
       </c>
       <c r="D166" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -4916,10 +4845,10 @@
         <v>PASS</v>
       </c>
       <c r="G166">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H166" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="167">
@@ -4930,7 +4859,7 @@
         <v>UNIT-166</v>
       </c>
       <c r="C167" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Calculate Distance Between Unit Domain</v>
       </c>
       <c r="D167" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -4942,10 +4871,10 @@
         <v>PASS</v>
       </c>
       <c r="G167">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H167" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="168">
@@ -4956,7 +4885,7 @@
         <v>UNIT-167</v>
       </c>
       <c r="C168" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Sort Doctors By Unit Domain</v>
       </c>
       <c r="D168" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -4968,10 +4897,10 @@
         <v>PASS</v>
       </c>
       <c r="G168">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H168" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="169">
@@ -4982,7 +4911,7 @@
         <v>UNIT-168</v>
       </c>
       <c r="C169" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Sort Doctors By Unit Domain</v>
       </c>
       <c r="D169" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -4997,7 +4926,7 @@
         <v>5</v>
       </c>
       <c r="H169" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="170">
@@ -5008,7 +4937,7 @@
         <v>UNIT-169</v>
       </c>
       <c r="C170" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Sort Doctors By Unit Domain</v>
       </c>
       <c r="D170" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5020,10 +4949,10 @@
         <v>PASS</v>
       </c>
       <c r="G170">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H170" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="171">
@@ -5034,7 +4963,7 @@
         <v>UNIT-170</v>
       </c>
       <c r="C171" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Calculate Doctor Average Unit Domain</v>
       </c>
       <c r="D171" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5046,10 +4975,10 @@
         <v>PASS</v>
       </c>
       <c r="G171">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H171" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="172">
@@ -5060,7 +4989,7 @@
         <v>UNIT-171</v>
       </c>
       <c r="C172" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Filter Slots By Unit Domain</v>
       </c>
       <c r="D172" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5075,7 +5004,7 @@
         <v>11</v>
       </c>
       <c r="H172" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="173">
@@ -5086,7 +5015,7 @@
         <v>UNIT-172</v>
       </c>
       <c r="C173" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Filter Slots By Unit Domain</v>
       </c>
       <c r="D173" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5098,10 +5027,10 @@
         <v>PASS</v>
       </c>
       <c r="G173">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H173" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="174">
@@ -5112,7 +5041,7 @@
         <v>UNIT-173</v>
       </c>
       <c r="C174" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Filter Slots By Unit Domain</v>
       </c>
       <c r="D174" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5124,10 +5053,10 @@
         <v>PASS</v>
       </c>
       <c r="G174">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H174" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="175">
@@ -5138,7 +5067,7 @@
         <v>UNIT-174</v>
       </c>
       <c r="C175" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Generate ICal (.ics) Unit Domain</v>
       </c>
       <c r="D175" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5153,7 +5082,7 @@
         <v>10</v>
       </c>
       <c r="H175" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="176">
@@ -5164,7 +5093,7 @@
         <v>UNIT-175</v>
       </c>
       <c r="C176" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Generate Google Calendar Unit Domain</v>
       </c>
       <c r="D176" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5179,7 +5108,7 @@
         <v>8</v>
       </c>
       <c r="H176" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="177">
@@ -5190,7 +5119,7 @@
         <v>UNIT-176</v>
       </c>
       <c r="C177" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Generate Outlook Calendar Unit Domain</v>
       </c>
       <c r="D177" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5202,10 +5131,10 @@
         <v>PASS</v>
       </c>
       <c r="G177">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H177" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="178">
@@ -5216,7 +5145,7 @@
         <v>UNIT-177</v>
       </c>
       <c r="C178" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Calculate Virtual Waiting Unit Domain</v>
       </c>
       <c r="D178" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5228,10 +5157,10 @@
         <v>PASS</v>
       </c>
       <c r="G178">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H178" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="179">
@@ -5242,7 +5171,7 @@
         <v>UNIT-178</v>
       </c>
       <c r="C179" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Calculate Estimated Wait Unit Domain</v>
       </c>
       <c r="D179" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5254,10 +5183,10 @@
         <v>PASS</v>
       </c>
       <c r="G179">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H179" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="180">
@@ -5268,7 +5197,7 @@
         <v>UNIT-179</v>
       </c>
       <c r="C180" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Telehealth Call Room Unit Domain</v>
       </c>
       <c r="D180" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5280,10 +5209,10 @@
         <v>PASS</v>
       </c>
       <c r="G180">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H180" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="181">
@@ -5294,7 +5223,7 @@
         <v>UNIT-180</v>
       </c>
       <c r="C181" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Patient Age Category Unit Domain</v>
       </c>
       <c r="D181" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5306,10 +5235,10 @@
         <v>PASS</v>
       </c>
       <c r="G181">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H181" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="182">
@@ -5320,7 +5249,7 @@
         <v>UNIT-181</v>
       </c>
       <c r="C182" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Procedure Required Time Unit Domain</v>
       </c>
       <c r="D182" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5335,7 +5264,7 @@
         <v>10</v>
       </c>
       <c r="H182" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="183">
@@ -5346,7 +5275,7 @@
         <v>UNIT-182</v>
       </c>
       <c r="C183" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Recurring Cleaning Interval Unit Domain</v>
       </c>
       <c r="D183" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5358,10 +5287,10 @@
         <v>PASS</v>
       </c>
       <c r="G183">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H183" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="184">
@@ -5372,7 +5301,7 @@
         <v>UNIT-183</v>
       </c>
       <c r="C184" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Follow-Up Visit Suggested Unit Domain</v>
       </c>
       <c r="D184" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5384,10 +5313,10 @@
         <v>PASS</v>
       </c>
       <c r="G184">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H184" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.915Z</v>
       </c>
     </row>
     <row r="185">
@@ -5398,7 +5327,7 @@
         <v>UNIT-184</v>
       </c>
       <c r="C185" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Check-In Window Activation Unit Domain</v>
       </c>
       <c r="D185" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5410,10 +5339,10 @@
         <v>PASS</v>
       </c>
       <c r="G185">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H185" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.916Z</v>
       </c>
     </row>
     <row r="186">
@@ -5424,7 +5353,7 @@
         <v>UNIT-185</v>
       </c>
       <c r="C186" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Online Payment Stripe Unit Domain</v>
       </c>
       <c r="D186" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5436,10 +5365,10 @@
         <v>PASS</v>
       </c>
       <c r="G186">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H186" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.916Z</v>
       </c>
     </row>
     <row r="187">
@@ -5450,7 +5379,7 @@
         <v>UNIT-186</v>
       </c>
       <c r="C187" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Discount Coupon Code Unit Domain</v>
       </c>
       <c r="D187" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5465,7 +5394,7 @@
         <v>10</v>
       </c>
       <c r="H187" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.916Z</v>
       </c>
     </row>
     <row r="188">
@@ -5476,7 +5405,7 @@
         <v>UNIT-187</v>
       </c>
       <c r="C188" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Family Member Multi-Booking Unit Domain</v>
       </c>
       <c r="D188" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5488,10 +5417,10 @@
         <v>PASS</v>
       </c>
       <c r="G188">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H188" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.916Z</v>
       </c>
     </row>
     <row r="189">
@@ -5502,7 +5431,7 @@
         <v>UNIT-188</v>
       </c>
       <c r="C189" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Doctor Daily Maximum Unit Domain</v>
       </c>
       <c r="D189" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5514,10 +5443,10 @@
         <v>PASS</v>
       </c>
       <c r="G189">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H189" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.916Z</v>
       </c>
     </row>
     <row r="190">
@@ -5528,7 +5457,7 @@
         <v>UNIT-189</v>
       </c>
       <c r="C190" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Doctor Shift Overtime Unit Domain</v>
       </c>
       <c r="D190" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5540,10 +5469,10 @@
         <v>PASS</v>
       </c>
       <c r="G190">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H190" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.916Z</v>
       </c>
     </row>
     <row r="191">
@@ -5554,7 +5483,7 @@
         <v>UNIT-190</v>
       </c>
       <c r="C191" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Clinic Operating Hours Unit Domain</v>
       </c>
       <c r="D191" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5566,10 +5495,10 @@
         <v>PASS</v>
       </c>
       <c r="G191">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H191" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.916Z</v>
       </c>
     </row>
     <row r="192">
@@ -5580,7 +5509,7 @@
         <v>UNIT-191</v>
       </c>
       <c r="C192" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Emergency Same-Day Priority Unit Domain</v>
       </c>
       <c r="D192" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5592,10 +5521,10 @@
         <v>PASS</v>
       </c>
       <c r="G192">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H192" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.916Z</v>
       </c>
     </row>
     <row r="193">
@@ -5606,7 +5535,7 @@
         <v>UNIT-192</v>
       </c>
       <c r="C193" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Calendar Slot Grid Unit Domain</v>
       </c>
       <c r="D193" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5618,10 +5547,10 @@
         <v>PASS</v>
       </c>
       <c r="G193">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H193" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.916Z</v>
       </c>
     </row>
     <row r="194">
@@ -5632,7 +5561,7 @@
         <v>UNIT-193</v>
       </c>
       <c r="C194" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Convert Time Slot Unit Domain</v>
       </c>
       <c r="D194" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5644,10 +5573,10 @@
         <v>PASS</v>
       </c>
       <c r="G194">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H194" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.916Z</v>
       </c>
     </row>
     <row r="195">
@@ -5658,7 +5587,7 @@
         <v>UNIT-194</v>
       </c>
       <c r="C195" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Calculate Total Revenue Unit Domain</v>
       </c>
       <c r="D195" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5670,10 +5599,10 @@
         <v>PASS</v>
       </c>
       <c r="G195">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H195" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.916Z</v>
       </c>
     </row>
     <row r="196">
@@ -5684,7 +5613,7 @@
         <v>UNIT-195</v>
       </c>
       <c r="C196" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Calculate Monthly No-Show Unit Domain</v>
       </c>
       <c r="D196" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5696,10 +5625,10 @@
         <v>PASS</v>
       </c>
       <c r="G196">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H196" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.916Z</v>
       </c>
     </row>
     <row r="197">
@@ -5710,7 +5639,7 @@
         <v>UNIT-196</v>
       </c>
       <c r="C197" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Calculate Clinic Capacity Unit Domain</v>
       </c>
       <c r="D197" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5722,10 +5651,10 @@
         <v>PASS</v>
       </c>
       <c r="G197">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H197" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.916Z</v>
       </c>
     </row>
     <row r="198">
@@ -5736,7 +5665,7 @@
         <v>UNIT-197</v>
       </c>
       <c r="C198" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Format Currency Display Unit Domain</v>
       </c>
       <c r="D198" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5748,10 +5677,10 @@
         <v>PASS</v>
       </c>
       <c r="G198">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H198" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.916Z</v>
       </c>
     </row>
     <row r="199">
@@ -5762,7 +5691,7 @@
         <v>UNIT-198</v>
       </c>
       <c r="C199" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Calculate Waiting List Unit Domain</v>
       </c>
       <c r="D199" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5774,10 +5703,10 @@
         <v>PASS</v>
       </c>
       <c r="G199">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H199" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.916Z</v>
       </c>
     </row>
     <row r="200">
@@ -5788,7 +5717,7 @@
         <v>UNIT-199</v>
       </c>
       <c r="C200" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Validate Insurance Member Unit Domain</v>
       </c>
       <c r="D200" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5800,10 +5729,10 @@
         <v>PASS</v>
       </c>
       <c r="G200">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H200" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.916Z</v>
       </c>
     </row>
     <row r="201">
@@ -5814,7 +5743,7 @@
         <v>UNIT-200</v>
       </c>
       <c r="C201" t="str">
-        <v>Appointment Distance &amp; Slot Calculators</v>
+        <v>Calculate Pre-Visit Questionnaire Unit Domain</v>
       </c>
       <c r="D201" t="str">
         <v>04_appointment_calculators.test.js</v>
@@ -5826,10 +5755,10 @@
         <v>PASS</v>
       </c>
       <c r="G201">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H201" t="str">
-        <v>2026-08-06T05:04:35.755Z</v>
+        <v>2026-08-06T05:06:54.916Z</v>
       </c>
     </row>
     <row r="202">
@@ -5840,7 +5769,7 @@
         <v>UNIT-201</v>
       </c>
       <c r="C202" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Image Aspect Ratio Unit Domain</v>
       </c>
       <c r="D202" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -5852,10 +5781,10 @@
         <v>PASS</v>
       </c>
       <c r="G202">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H202" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.920Z</v>
       </c>
     </row>
     <row r="203">
@@ -5866,7 +5795,7 @@
         <v>UNIT-202</v>
       </c>
       <c r="C203" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Resize Image Max Unit Domain</v>
       </c>
       <c r="D203" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -5878,10 +5807,10 @@
         <v>PASS</v>
       </c>
       <c r="G203">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H203" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="204">
@@ -5892,7 +5821,7 @@
         <v>UNIT-203</v>
       </c>
       <c r="C204" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Image Pixel Contrast Unit Domain</v>
       </c>
       <c r="D204" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -5904,10 +5833,10 @@
         <v>PASS</v>
       </c>
       <c r="G204">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H204" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="205">
@@ -5918,7 +5847,7 @@
         <v>UNIT-204</v>
       </c>
       <c r="C205" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Grayscale Color Conversion Unit Domain</v>
       </c>
       <c r="D205" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -5930,10 +5859,10 @@
         <v>PASS</v>
       </c>
       <c r="G205">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H205" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="206">
@@ -5944,7 +5873,7 @@
         <v>UNIT-205</v>
       </c>
       <c r="C206" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Calculate Image Sharpness Unit Domain</v>
       </c>
       <c r="D206" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -5956,10 +5885,10 @@
         <v>PASS</v>
       </c>
       <c r="G206">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H206" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="207">
@@ -5970,7 +5899,7 @@
         <v>UNIT-206</v>
       </c>
       <c r="C207" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Reject Blurry Photos Unit Domain</v>
       </c>
       <c r="D207" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -5982,10 +5911,10 @@
         <v>PASS</v>
       </c>
       <c r="G207">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H207" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="208">
@@ -5996,7 +5925,7 @@
         <v>UNIT-207</v>
       </c>
       <c r="C208" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Calculate Bounding Box Unit Domain</v>
       </c>
       <c r="D208" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6011,7 +5940,7 @@
         <v>10</v>
       </c>
       <c r="H208" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="209">
@@ -6022,7 +5951,7 @@
         <v>UNIT-208</v>
       </c>
       <c r="C209" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Bounding Box Area Unit Domain</v>
       </c>
       <c r="D209" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6034,10 +5963,10 @@
         <v>PASS</v>
       </c>
       <c r="G209">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H209" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="210">
@@ -6048,7 +5977,7 @@
         <v>UNIT-209</v>
       </c>
       <c r="C210" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Normalize Bounding Box Unit Domain</v>
       </c>
       <c r="D210" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6060,10 +5989,10 @@
         <v>PASS</v>
       </c>
       <c r="G210">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H210" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="211">
@@ -6074,7 +6003,7 @@
         <v>UNIT-210</v>
       </c>
       <c r="C211" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Denormalize Bounding Box Unit Domain</v>
       </c>
       <c r="D211" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6086,10 +6015,10 @@
         <v>PASS</v>
       </c>
       <c r="G211">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H211" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="212">
@@ -6100,7 +6029,7 @@
         <v>UNIT-211</v>
       </c>
       <c r="C212" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Convert DICOM Window Unit Domain</v>
       </c>
       <c r="D212" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6112,10 +6041,10 @@
         <v>PASS</v>
       </c>
       <c r="G212">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H212" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="213">
@@ -6126,7 +6055,7 @@
         <v>UNIT-212</v>
       </c>
       <c r="C213" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Extract DICOM Metadata Unit Domain</v>
       </c>
       <c r="D213" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6138,10 +6067,10 @@
         <v>PASS</v>
       </c>
       <c r="G213">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H213" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="214">
@@ -6152,7 +6081,7 @@
         <v>UNIT-213</v>
       </c>
       <c r="C214" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Image Rotation Matrix Unit Domain</v>
       </c>
       <c r="D214" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6164,10 +6093,10 @@
         <v>PASS</v>
       </c>
       <c r="G214">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H214" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="215">
@@ -6178,7 +6107,7 @@
         <v>UNIT-214</v>
       </c>
       <c r="C215" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Image Horizontal Flip Unit Domain</v>
       </c>
       <c r="D215" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6190,10 +6119,10 @@
         <v>PASS</v>
       </c>
       <c r="G215">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H215" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="216">
@@ -6204,7 +6133,7 @@
         <v>UNIT-215</v>
       </c>
       <c r="C216" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Crop Image Sub-region Unit Domain</v>
       </c>
       <c r="D216" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6216,10 +6145,10 @@
         <v>PASS</v>
       </c>
       <c r="G216">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H216" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="217">
@@ -6230,7 +6159,7 @@
         <v>UNIT-216</v>
       </c>
       <c r="C217" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Calculate Heatmap Color Unit Domain</v>
       </c>
       <c r="D217" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6242,10 +6171,10 @@
         <v>PASS</v>
       </c>
       <c r="G217">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H217" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="218">
@@ -6256,7 +6185,7 @@
         <v>UNIT-217</v>
       </c>
       <c r="C218" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Overlay Mask Alpha Unit Domain</v>
       </c>
       <c r="D218" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6268,10 +6197,10 @@
         <v>PASS</v>
       </c>
       <c r="G218">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H218" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="219">
@@ -6282,7 +6211,7 @@
         <v>UNIT-218</v>
       </c>
       <c r="C219" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Tooth FDI Bounding Unit Domain</v>
       </c>
       <c r="D219" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6294,10 +6223,10 @@
         <v>PASS</v>
       </c>
       <c r="G219">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H219" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="220">
@@ -6308,7 +6237,7 @@
         <v>UNIT-219</v>
       </c>
       <c r="C220" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Tooth Universal Bounding Unit Domain</v>
       </c>
       <c r="D220" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6323,7 +6252,7 @@
         <v>7</v>
       </c>
       <c r="H220" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="221">
@@ -6334,7 +6263,7 @@
         <v>UNIT-220</v>
       </c>
       <c r="C221" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Detect Over-exposed Pure Unit Domain</v>
       </c>
       <c r="D221" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6349,7 +6278,7 @@
         <v>6</v>
       </c>
       <c r="H221" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="222">
@@ -6360,7 +6289,7 @@
         <v>UNIT-221</v>
       </c>
       <c r="C222" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Detect Under-exposed Pure Unit Domain</v>
       </c>
       <c r="D222" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6372,10 +6301,10 @@
         <v>PASS</v>
       </c>
       <c r="G222">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H222" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="223">
@@ -6386,7 +6315,7 @@
         <v>UNIT-222</v>
       </c>
       <c r="C223" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Calculate Mean Pixel Unit Domain</v>
       </c>
       <c r="D223" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6398,10 +6327,10 @@
         <v>PASS</v>
       </c>
       <c r="G223">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H223" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="224">
@@ -6412,7 +6341,7 @@
         <v>UNIT-223</v>
       </c>
       <c r="C224" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Calculate Standard Deviation Unit Domain</v>
       </c>
       <c r="D224" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6424,10 +6353,10 @@
         <v>PASS</v>
       </c>
       <c r="G224">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H224" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="225">
@@ -6438,7 +6367,7 @@
         <v>UNIT-224</v>
       </c>
       <c r="C225" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Compress JPEG Quality Unit Domain</v>
       </c>
       <c r="D225" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6450,10 +6379,10 @@
         <v>PASS</v>
       </c>
       <c r="G225">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H225" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="226">
@@ -6464,7 +6393,7 @@
         <v>UNIT-225</v>
       </c>
       <c r="C226" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Convert Raw Image Unit Domain</v>
       </c>
       <c r="D226" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6476,10 +6405,10 @@
         <v>PASS</v>
       </c>
       <c r="G226">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H226" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="227">
@@ -6490,7 +6419,7 @@
         <v>UNIT-226</v>
       </c>
       <c r="C227" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Convert Base64 String Unit Domain</v>
       </c>
       <c r="D227" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6502,10 +6431,10 @@
         <v>PASS</v>
       </c>
       <c r="G227">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H227" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="228">
@@ -6516,7 +6445,7 @@
         <v>UNIT-227</v>
       </c>
       <c r="C228" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Validate Image File Unit Domain</v>
       </c>
       <c r="D228" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6528,10 +6457,10 @@
         <v>PASS</v>
       </c>
       <c r="G228">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H228" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="229">
@@ -6542,7 +6471,7 @@
         <v>UNIT-228</v>
       </c>
       <c r="C229" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Calculate Image SHA-256 Unit Domain</v>
       </c>
       <c r="D229" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6554,10 +6483,10 @@
         <v>PASS</v>
       </c>
       <c r="G229">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H229" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="230">
@@ -6568,7 +6497,7 @@
         <v>UNIT-229</v>
       </c>
       <c r="C230" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Extract Exif Camera Unit Domain</v>
       </c>
       <c r="D230" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6580,10 +6509,10 @@
         <v>PASS</v>
       </c>
       <c r="G230">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H230" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="231">
@@ -6594,7 +6523,7 @@
         <v>UNIT-230</v>
       </c>
       <c r="C231" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Strip Sensitive Exif Unit Domain</v>
       </c>
       <c r="D231" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6606,10 +6535,10 @@
         <v>PASS</v>
       </c>
       <c r="G231">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H231" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="232">
@@ -6620,7 +6549,7 @@
         <v>UNIT-231</v>
       </c>
       <c r="C232" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Generate Thumbnail Preview Unit Domain</v>
       </c>
       <c r="D232" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6632,10 +6561,10 @@
         <v>PASS</v>
       </c>
       <c r="G232">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H232" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="233">
@@ -6646,7 +6575,7 @@
         <v>UNIT-232</v>
       </c>
       <c r="C233" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Color Histogram Frequency Unit Domain</v>
       </c>
       <c r="D233" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6658,10 +6587,10 @@
         <v>PASS</v>
       </c>
       <c r="G233">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H233" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="234">
@@ -6672,7 +6601,7 @@
         <v>UNIT-233</v>
       </c>
       <c r="C234" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Detect Oral Cavity Unit Domain</v>
       </c>
       <c r="D234" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6684,10 +6613,10 @@
         <v>PASS</v>
       </c>
       <c r="G234">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H234" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="235">
@@ -6698,7 +6627,7 @@
         <v>UNIT-234</v>
       </c>
       <c r="C235" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Classify Intraoral Photo Unit Domain</v>
       </c>
       <c r="D235" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6710,10 +6639,10 @@
         <v>PASS</v>
       </c>
       <c r="G235">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H235" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="236">
@@ -6724,7 +6653,7 @@
         <v>UNIT-235</v>
       </c>
       <c r="C236" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Classify Bite-wing Vs Unit Domain</v>
       </c>
       <c r="D236" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6739,7 +6668,7 @@
         <v>3</v>
       </c>
       <c r="H236" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="237">
@@ -6750,7 +6679,7 @@
         <v>UNIT-236</v>
       </c>
       <c r="C237" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Calculate Dental Cavity Unit Domain</v>
       </c>
       <c r="D237" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6762,10 +6691,10 @@
         <v>PASS</v>
       </c>
       <c r="G237">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H237" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="238">
@@ -6776,7 +6705,7 @@
         <v>UNIT-237</v>
       </c>
       <c r="C238" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Calculate Plaque Coverage Unit Domain</v>
       </c>
       <c r="D238" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6788,10 +6717,10 @@
         <v>PASS</v>
       </c>
       <c r="G238">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H238" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="239">
@@ -6802,7 +6731,7 @@
         <v>UNIT-238</v>
       </c>
       <c r="C239" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Calculate Gingivitis Inflammation Unit Domain</v>
       </c>
       <c r="D239" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6814,10 +6743,10 @@
         <v>PASS</v>
       </c>
       <c r="G239">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H239" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="240">
@@ -6828,7 +6757,7 @@
         <v>UNIT-239</v>
       </c>
       <c r="C240" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Enamel Crack Line Unit Domain</v>
       </c>
       <c r="D240" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6840,10 +6769,10 @@
         <v>PASS</v>
       </c>
       <c r="G240">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H240" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="241">
@@ -6854,7 +6783,7 @@
         <v>UNIT-240</v>
       </c>
       <c r="C241" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Measure Pixel Distance Unit Domain</v>
       </c>
       <c r="D241" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6866,10 +6795,10 @@
         <v>PASS</v>
       </c>
       <c r="G241">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H241" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="242">
@@ -6880,7 +6809,7 @@
         <v>UNIT-241</v>
       </c>
       <c r="C242" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Convert Pixel Distance Unit Domain</v>
       </c>
       <c r="D242" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6892,10 +6821,10 @@
         <v>PASS</v>
       </c>
       <c r="G242">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H242" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="243">
@@ -6906,7 +6835,7 @@
         <v>UNIT-242</v>
       </c>
       <c r="C243" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Calculate Cobb Angle Unit Domain</v>
       </c>
       <c r="D243" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6918,10 +6847,10 @@
         <v>PASS</v>
       </c>
       <c r="G243">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H243" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="244">
@@ -6932,7 +6861,7 @@
         <v>UNIT-243</v>
       </c>
       <c r="C244" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Magnifying Glass Crop Unit Domain</v>
       </c>
       <c r="D244" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6944,10 +6873,10 @@
         <v>PASS</v>
       </c>
       <c r="G244">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H244" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="245">
@@ -6958,7 +6887,7 @@
         <v>UNIT-244</v>
       </c>
       <c r="C245" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Negative Film Invert Unit Domain</v>
       </c>
       <c r="D245" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6970,10 +6899,10 @@
         <v>PASS</v>
       </c>
       <c r="G245">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H245" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="246">
@@ -6984,7 +6913,7 @@
         <v>UNIT-245</v>
       </c>
       <c r="C246" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Add Watermark Text Unit Domain</v>
       </c>
       <c r="D246" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -6996,10 +6925,10 @@
         <v>PASS</v>
       </c>
       <c r="G246">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H246" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="247">
@@ -7010,7 +6939,7 @@
         <v>UNIT-246</v>
       </c>
       <c r="C247" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Calculate Image Compression Unit Domain</v>
       </c>
       <c r="D247" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -7022,10 +6951,10 @@
         <v>PASS</v>
       </c>
       <c r="G247">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H247" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="248">
@@ -7036,7 +6965,7 @@
         <v>UNIT-247</v>
       </c>
       <c r="C248" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Validate DICOM File Unit Domain</v>
       </c>
       <c r="D248" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -7048,10 +6977,10 @@
         <v>PASS</v>
       </c>
       <c r="G248">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H248" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="249">
@@ -7062,7 +6991,7 @@
         <v>UNIT-248</v>
       </c>
       <c r="C249" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Batch Image Array Unit Domain</v>
       </c>
       <c r="D249" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -7074,10 +7003,10 @@
         <v>PASS</v>
       </c>
       <c r="G249">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H249" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.921Z</v>
       </c>
     </row>
     <row r="250">
@@ -7088,7 +7017,7 @@
         <v>UNIT-249</v>
       </c>
       <c r="C250" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Multi-Scale Feature Pyramid Unit Domain</v>
       </c>
       <c r="D250" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -7100,10 +7029,10 @@
         <v>PASS</v>
       </c>
       <c r="G250">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H250" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.922Z</v>
       </c>
     </row>
     <row r="251">
@@ -7114,7 +7043,7 @@
         <v>UNIT-250</v>
       </c>
       <c r="C251" t="str">
-        <v>Vision Image Preprocessors</v>
+        <v>Validate Canvas Context Unit Domain</v>
       </c>
       <c r="D251" t="str">
         <v>05_vision_preprocessors.test.js</v>
@@ -7126,10 +7055,10 @@
         <v>PASS</v>
       </c>
       <c r="G251">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H251" t="str">
-        <v>2026-08-06T05:04:35.757Z</v>
+        <v>2026-08-06T05:06:54.922Z</v>
       </c>
     </row>
     <row r="252">
@@ -7140,7 +7069,7 @@
         <v>UNIT-251</v>
       </c>
       <c r="C252" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Argon2id Password Salt Unit Domain</v>
       </c>
       <c r="D252" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7152,10 +7081,10 @@
         <v>PASS</v>
       </c>
       <c r="G252">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H252" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="253">
@@ -7166,7 +7095,7 @@
         <v>UNIT-252</v>
       </c>
       <c r="C253" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Bcrypt Password Hash Unit Domain</v>
       </c>
       <c r="D253" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7178,10 +7107,10 @@
         <v>PASS</v>
       </c>
       <c r="G253">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H253" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="254">
@@ -7192,7 +7121,7 @@
         <v>UNIT-253</v>
       </c>
       <c r="C254" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Generate Random Cryptographic Unit Domain</v>
       </c>
       <c r="D254" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7207,7 +7136,7 @@
         <v>2</v>
       </c>
       <c r="H254" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="255">
@@ -7218,7 +7147,7 @@
         <v>UNIT-254</v>
       </c>
       <c r="C255" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>AES-256-GCM Encryption Payload Unit Domain</v>
       </c>
       <c r="D255" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7230,10 +7159,10 @@
         <v>PASS</v>
       </c>
       <c r="G255">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H255" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="256">
@@ -7244,7 +7173,7 @@
         <v>UNIT-255</v>
       </c>
       <c r="C256" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>AES-256-GCM Decryption Payload Unit Domain</v>
       </c>
       <c r="D256" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7256,10 +7185,10 @@
         <v>PASS</v>
       </c>
       <c r="G256">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H256" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="257">
@@ -7270,7 +7199,7 @@
         <v>UNIT-256</v>
       </c>
       <c r="C257" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Validate Authenticated Encryption Unit Domain</v>
       </c>
       <c r="D257" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7282,10 +7211,10 @@
         <v>PASS</v>
       </c>
       <c r="G257">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H257" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="258">
@@ -7296,7 +7225,7 @@
         <v>UNIT-257</v>
       </c>
       <c r="C258" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>JWT Sign Access Unit Domain</v>
       </c>
       <c r="D258" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7308,10 +7237,10 @@
         <v>PASS</v>
       </c>
       <c r="G258">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H258" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="259">
@@ -7322,7 +7251,7 @@
         <v>UNIT-258</v>
       </c>
       <c r="C259" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>JWT Verify Access Unit Domain</v>
       </c>
       <c r="D259" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7334,10 +7263,10 @@
         <v>PASS</v>
       </c>
       <c r="G259">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H259" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="260">
@@ -7348,7 +7277,7 @@
         <v>UNIT-259</v>
       </c>
       <c r="C260" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>JWT Decode Header Unit Domain</v>
       </c>
       <c r="D260" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7360,10 +7289,10 @@
         <v>PASS</v>
       </c>
       <c r="G260">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H260" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="261">
@@ -7374,7 +7303,7 @@
         <v>UNIT-260</v>
       </c>
       <c r="C261" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>JWT Expiration Time Unit Domain</v>
       </c>
       <c r="D261" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7386,10 +7315,10 @@
         <v>PASS</v>
       </c>
       <c r="G261">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H261" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="262">
@@ -7400,7 +7329,7 @@
         <v>UNIT-261</v>
       </c>
       <c r="C262" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>JWT Not Before Unit Domain</v>
       </c>
       <c r="D262" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7412,10 +7341,10 @@
         <v>PASS</v>
       </c>
       <c r="G262">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H262" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="263">
@@ -7426,7 +7355,7 @@
         <v>UNIT-262</v>
       </c>
       <c r="C263" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>JWT Token Fingerprint Unit Domain</v>
       </c>
       <c r="D263" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7438,10 +7367,10 @@
         <v>PASS</v>
       </c>
       <c r="G263">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H263" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="264">
@@ -7452,7 +7381,7 @@
         <v>UNIT-263</v>
       </c>
       <c r="C264" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Sanitize HTML String Unit Domain</v>
       </c>
       <c r="D264" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7464,10 +7393,10 @@
         <v>PASS</v>
       </c>
       <c r="G264">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H264" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="265">
@@ -7478,7 +7407,7 @@
         <v>UNIT-264</v>
       </c>
       <c r="C265" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Sanitize HTML String Unit Domain</v>
       </c>
       <c r="D265" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7490,10 +7419,10 @@
         <v>PASS</v>
       </c>
       <c r="G265">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H265" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="266">
@@ -7504,7 +7433,7 @@
         <v>UNIT-265</v>
       </c>
       <c r="C266" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Escape SQL Special Unit Domain</v>
       </c>
       <c r="D266" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7516,10 +7445,10 @@
         <v>PASS</v>
       </c>
       <c r="G266">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H266" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="267">
@@ -7530,7 +7459,7 @@
         <v>UNIT-266</v>
       </c>
       <c r="C267" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Validate Email Address Unit Domain</v>
       </c>
       <c r="D267" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7542,10 +7471,10 @@
         <v>PASS</v>
       </c>
       <c r="G267">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H267" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="268">
@@ -7556,7 +7485,7 @@
         <v>UNIT-267</v>
       </c>
       <c r="C268" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Validate Phone Number Unit Domain</v>
       </c>
       <c r="D268" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7568,10 +7497,10 @@
         <v>PASS</v>
       </c>
       <c r="G268">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H268" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="269">
@@ -7582,7 +7511,7 @@
         <v>UNIT-268</v>
       </c>
       <c r="C269" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Sliding Window Rate Unit Domain</v>
       </c>
       <c r="D269" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7594,10 +7523,10 @@
         <v>PASS</v>
       </c>
       <c r="G269">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H269" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="270">
@@ -7608,7 +7537,7 @@
         <v>UNIT-269</v>
       </c>
       <c r="C270" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Token Bucket Rate Unit Domain</v>
       </c>
       <c r="D270" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7620,10 +7549,10 @@
         <v>PASS</v>
       </c>
       <c r="G270">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H270" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="271">
@@ -7634,7 +7563,7 @@
         <v>UNIT-270</v>
       </c>
       <c r="C271" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>HTTP Header Security Unit Domain</v>
       </c>
       <c r="D271" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7646,10 +7575,10 @@
         <v>PASS</v>
       </c>
       <c r="G271">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H271" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="272">
@@ -7660,7 +7589,7 @@
         <v>UNIT-271</v>
       </c>
       <c r="C272" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>CORS Origin Whitelist Unit Domain</v>
       </c>
       <c r="D272" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7672,10 +7601,10 @@
         <v>PASS</v>
       </c>
       <c r="G272">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H272" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="273">
@@ -7686,7 +7615,7 @@
         <v>UNIT-272</v>
       </c>
       <c r="C273" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>CSRF Double Submit Unit Domain</v>
       </c>
       <c r="D273" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7698,10 +7627,10 @@
         <v>PASS</v>
       </c>
       <c r="G273">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H273" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="274">
@@ -7712,7 +7641,7 @@
         <v>UNIT-273</v>
       </c>
       <c r="C274" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Constant Time String Unit Domain</v>
       </c>
       <c r="D274" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7724,10 +7653,10 @@
         <v>PASS</v>
       </c>
       <c r="G274">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H274" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="275">
@@ -7738,7 +7667,7 @@
         <v>UNIT-274</v>
       </c>
       <c r="C275" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Generate TOTP 6-Digit Unit Domain</v>
       </c>
       <c r="D275" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7750,10 +7679,10 @@
         <v>PASS</v>
       </c>
       <c r="G275">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H275" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="276">
@@ -7764,7 +7693,7 @@
         <v>UNIT-275</v>
       </c>
       <c r="C276" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Verify TOTP 6-Digit Unit Domain</v>
       </c>
       <c r="D276" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7776,10 +7705,10 @@
         <v>PASS</v>
       </c>
       <c r="G276">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H276" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="277">
@@ -7790,7 +7719,7 @@
         <v>UNIT-276</v>
       </c>
       <c r="C277" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Generate QR Code Unit Domain</v>
       </c>
       <c r="D277" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7802,10 +7731,10 @@
         <v>PASS</v>
       </c>
       <c r="G277">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H277" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="278">
@@ -7816,7 +7745,7 @@
         <v>UNIT-277</v>
       </c>
       <c r="C278" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>IP Address Subnet Unit Domain</v>
       </c>
       <c r="D278" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7828,10 +7757,10 @@
         <v>PASS</v>
       </c>
       <c r="G278">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H278" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="279">
@@ -7842,7 +7771,7 @@
         <v>UNIT-278</v>
       </c>
       <c r="C279" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Anonymize IP Address Unit Domain</v>
       </c>
       <c r="D279" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7854,10 +7783,10 @@
         <v>PASS</v>
       </c>
       <c r="G279">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H279" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="280">
@@ -7868,7 +7797,7 @@
         <v>UNIT-279</v>
       </c>
       <c r="C280" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Mask Credit Card Unit Domain</v>
       </c>
       <c r="D280" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7880,10 +7809,10 @@
         <v>PASS</v>
       </c>
       <c r="G280">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H280" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="281">
@@ -7894,7 +7823,7 @@
         <v>UNIT-280</v>
       </c>
       <c r="C281" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Mask Social Security Unit Domain</v>
       </c>
       <c r="D281" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7906,10 +7835,10 @@
         <v>PASS</v>
       </c>
       <c r="G281">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H281" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="282">
@@ -7920,7 +7849,7 @@
         <v>UNIT-281</v>
       </c>
       <c r="C282" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Mask Patient Email Unit Domain</v>
       </c>
       <c r="D282" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7932,10 +7861,10 @@
         <v>PASS</v>
       </c>
       <c r="G282">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H282" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="283">
@@ -7946,7 +7875,7 @@
         <v>UNIT-282</v>
       </c>
       <c r="C283" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Validate Password Complexity Unit Domain</v>
       </c>
       <c r="D283" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7958,10 +7887,10 @@
         <v>PASS</v>
       </c>
       <c r="G283">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H283" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="284">
@@ -7972,7 +7901,7 @@
         <v>UNIT-283</v>
       </c>
       <c r="C284" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Calculate Password Strength Unit Domain</v>
       </c>
       <c r="D284" t="str">
         <v>06_security_crypto.test.js</v>
@@ -7984,10 +7913,10 @@
         <v>PASS</v>
       </c>
       <c r="G284">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H284" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="285">
@@ -7998,7 +7927,7 @@
         <v>UNIT-284</v>
       </c>
       <c r="C285" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Detect Leaked Password Unit Domain</v>
       </c>
       <c r="D285" t="str">
         <v>06_security_crypto.test.js</v>
@@ -8010,10 +7939,10 @@
         <v>PASS</v>
       </c>
       <c r="G285">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H285" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="286">
@@ -8024,7 +7953,7 @@
         <v>UNIT-285</v>
       </c>
       <c r="C286" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Generate Random Strong Unit Domain</v>
       </c>
       <c r="D286" t="str">
         <v>06_security_crypto.test.js</v>
@@ -8036,10 +7965,10 @@
         <v>PASS</v>
       </c>
       <c r="G286">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H286" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="287">
@@ -8050,7 +7979,7 @@
         <v>UNIT-286</v>
       </c>
       <c r="C287" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Validate Audit Log Unit Domain</v>
       </c>
       <c r="D287" t="str">
         <v>06_security_crypto.test.js</v>
@@ -8062,10 +7991,10 @@
         <v>PASS</v>
       </c>
       <c r="G287">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H287" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="288">
@@ -8076,7 +8005,7 @@
         <v>UNIT-287</v>
       </c>
       <c r="C288" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Verify File Upload Unit Domain</v>
       </c>
       <c r="D288" t="str">
         <v>06_security_crypto.test.js</v>
@@ -8088,10 +8017,10 @@
         <v>PASS</v>
       </c>
       <c r="G288">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H288" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="289">
@@ -8102,7 +8031,7 @@
         <v>UNIT-288</v>
       </c>
       <c r="C289" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Sanitize File Name Unit Domain</v>
       </c>
       <c r="D289" t="str">
         <v>06_security_crypto.test.js</v>
@@ -8114,10 +8043,10 @@
         <v>PASS</v>
       </c>
       <c r="G289">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H289" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="290">
@@ -8128,7 +8057,7 @@
         <v>UNIT-289</v>
       </c>
       <c r="C290" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Strip Control Characters Unit Domain</v>
       </c>
       <c r="D290" t="str">
         <v>06_security_crypto.test.js</v>
@@ -8140,10 +8069,10 @@
         <v>PASS</v>
       </c>
       <c r="G290">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H290" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="291">
@@ -8154,7 +8083,7 @@
         <v>UNIT-290</v>
       </c>
       <c r="C291" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Sanitize JSON Payload Unit Domain</v>
       </c>
       <c r="D291" t="str">
         <v>06_security_crypto.test.js</v>
@@ -8166,10 +8095,10 @@
         <v>PASS</v>
       </c>
       <c r="G291">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H291" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="292">
@@ -8180,7 +8109,7 @@
         <v>UNIT-291</v>
       </c>
       <c r="C292" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>PBKDF2 Key Derivation Unit Domain</v>
       </c>
       <c r="D292" t="str">
         <v>06_security_crypto.test.js</v>
@@ -8195,7 +8124,7 @@
         <v>2</v>
       </c>
       <c r="H292" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="293">
@@ -8206,7 +8135,7 @@
         <v>UNIT-292</v>
       </c>
       <c r="C293" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>RSA 2048-Bit Public Unit Domain</v>
       </c>
       <c r="D293" t="str">
         <v>06_security_crypto.test.js</v>
@@ -8218,10 +8147,10 @@
         <v>PASS</v>
       </c>
       <c r="G293">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H293" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="294">
@@ -8232,7 +8161,7 @@
         <v>UNIT-293</v>
       </c>
       <c r="C294" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>ECDSA P-256 Elliptic Unit Domain</v>
       </c>
       <c r="D294" t="str">
         <v>06_security_crypto.test.js</v>
@@ -8244,10 +8173,10 @@
         <v>PASS</v>
       </c>
       <c r="G294">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H294" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="295">
@@ -8258,7 +8187,7 @@
         <v>UNIT-294</v>
       </c>
       <c r="C295" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Secure Memory Erasure Unit Domain</v>
       </c>
       <c r="D295" t="str">
         <v>06_security_crypto.test.js</v>
@@ -8270,10 +8199,10 @@
         <v>PASS</v>
       </c>
       <c r="G295">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H295" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="296">
@@ -8284,7 +8213,7 @@
         <v>UNIT-295</v>
       </c>
       <c r="C296" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Validate Session Cookie Unit Domain</v>
       </c>
       <c r="D296" t="str">
         <v>06_security_crypto.test.js</v>
@@ -8296,10 +8225,10 @@
         <v>PASS</v>
       </c>
       <c r="G296">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H296" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="297">
@@ -8310,7 +8239,7 @@
         <v>UNIT-296</v>
       </c>
       <c r="C297" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Detect Brute Force Unit Domain</v>
       </c>
       <c r="D297" t="str">
         <v>06_security_crypto.test.js</v>
@@ -8322,10 +8251,10 @@
         <v>PASS</v>
       </c>
       <c r="G297">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H297" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="298">
@@ -8336,7 +8265,7 @@
         <v>UNIT-297</v>
       </c>
       <c r="C298" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Calculate Account Lockout Unit Domain</v>
       </c>
       <c r="D298" t="str">
         <v>06_security_crypto.test.js</v>
@@ -8348,10 +8277,10 @@
         <v>PASS</v>
       </c>
       <c r="G298">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H298" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="299">
@@ -8362,7 +8291,7 @@
         <v>UNIT-298</v>
       </c>
       <c r="C299" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Role Permission Bitwise Unit Domain</v>
       </c>
       <c r="D299" t="str">
         <v>06_security_crypto.test.js</v>
@@ -8374,10 +8303,10 @@
         <v>PASS</v>
       </c>
       <c r="G299">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H299" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="300">
@@ -8388,7 +8317,7 @@
         <v>UNIT-299</v>
       </c>
       <c r="C300" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Validate API Key Unit Domain</v>
       </c>
       <c r="D300" t="str">
         <v>06_security_crypto.test.js</v>
@@ -8400,10 +8329,10 @@
         <v>PASS</v>
       </c>
       <c r="G300">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H300" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
     <row r="301">
@@ -8414,7 +8343,7 @@
         <v>UNIT-300</v>
       </c>
       <c r="C301" t="str">
-        <v>Security Cryptography Engine</v>
+        <v>Sanitize Logs - Unit Domain</v>
       </c>
       <c r="D301" t="str">
         <v>06_security_crypto.test.js</v>
@@ -8426,10 +8355,10 @@
         <v>PASS</v>
       </c>
       <c r="G301">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H301" t="str">
-        <v>2026-08-06T05:04:35.760Z</v>
+        <v>2026-08-06T05:06:54.927Z</v>
       </c>
     </row>
   </sheetData>
